--- a/Top_TFs_pathways_F23_merged.xlsx
+++ b/Top_TFs_pathways_F23_merged.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve">pathway</t>
   </si>
@@ -173,52 +173,46 @@
     <t xml:space="preserve">KLF13</t>
   </si>
   <si>
-    <t xml:space="preserve">HALLMARK_ESTROGEN_RESPONSE_LATE</t>
+    <t xml:space="preserve">HALLMARK_FATTY_ACID_METABOLISM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HIF1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_HYPOXIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
   </si>
   <si>
     <t xml:space="preserve">IRF4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCF7L2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_FATTY_ACID_METABOLISM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIF1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_HYPOXIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
   </si>
   <si>
     <t xml:space="preserve">STAT4</t>
@@ -2867,28 +2861,26 @@
         <v>53</v>
       </c>
       <c r="B82" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.568852661112965</v>
       </c>
       <c r="E82" t="n">
-        <v>-2.89999694915305</v>
+        <v>1.69911620492032</v>
       </c>
       <c r="F82" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G82" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0892972906656036</v>
+      </c>
+      <c r="G82"/>
       <c r="H82" t="n">
-        <v>4.10121501633284</v>
+        <v>1.69911620492032</v>
       </c>
       <c r="I82" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="83">
@@ -2896,23 +2888,25 @@
         <v>53</v>
       </c>
       <c r="B83" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C83" t="n">
         <v>2</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.127705649007195</v>
       </c>
       <c r="E83" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.02792198997847</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G83"/>
+        <v>0.303986524655079</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.763093745018922</v>
+      </c>
       <c r="H83" t="n">
-        <v>3.1115168358807</v>
+        <v>1.4537012192891</v>
       </c>
       <c r="I83" t="s">
         <v>11</v>
@@ -2923,25 +2917,23 @@
         <v>53</v>
       </c>
       <c r="B84" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.449306074582525</v>
       </c>
       <c r="E84" t="n">
-        <v>-2.09437444905346</v>
+        <v>-0.843128119908009</v>
       </c>
       <c r="F84" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G84" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.39915679353664</v>
+      </c>
+      <c r="G84"/>
       <c r="H84" t="n">
-        <v>2.96189275053909</v>
+        <v>1.19236322199204</v>
       </c>
       <c r="I84" t="s">
         <v>11</v>
@@ -2952,26 +2944,26 @@
         <v>53</v>
       </c>
       <c r="B85" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C85" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D85" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.141237121743142</v>
       </c>
       <c r="E85" t="n">
-        <v>1.84413569483074</v>
+        <v>-0.505075071717537</v>
       </c>
       <c r="F85" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.613506109324499</v>
       </c>
       <c r="G85"/>
       <c r="H85" t="n">
-        <v>2.60800171048597</v>
+        <v>1.01015014343507</v>
       </c>
       <c r="I85" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="86">
@@ -2979,23 +2971,25 @@
         <v>53</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0.202760189088342</v>
+        <v>0.0728339894275881</v>
       </c>
       <c r="E86" t="n">
-        <v>1.0082954236419</v>
+        <v>0.706727814492832</v>
       </c>
       <c r="F86" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G86"/>
+        <v>0.47973564103236</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.870332217592113</v>
+      </c>
       <c r="H86" t="n">
-        <v>2.25461710866525</v>
+        <v>0.706727814492832</v>
       </c>
       <c r="I86" t="s">
         <v>13</v>
@@ -3006,25 +3000,23 @@
         <v>53</v>
       </c>
       <c r="B87" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.235951201675001</v>
+        <v>-0.0813258659038187</v>
       </c>
       <c r="E87" t="n">
-        <v>-1.80370004209605</v>
+        <v>-0.382914639728419</v>
       </c>
       <c r="F87" t="n">
-        <v>0.0712783429559855</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.503626901967002</v>
-      </c>
+        <v>0.701783056225352</v>
+      </c>
+      <c r="G87"/>
       <c r="H87" t="n">
-        <v>1.80370004209605</v>
+        <v>0.382914639728419</v>
       </c>
       <c r="I87" t="s">
         <v>11</v>
@@ -3035,26 +3027,26 @@
         <v>53</v>
       </c>
       <c r="B88" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D88" t="n">
-        <v>-0.582671827903238</v>
+        <v>0.0417765291221938</v>
       </c>
       <c r="E88" t="n">
-        <v>-1.73074764769325</v>
+        <v>0.213160526557962</v>
       </c>
       <c r="F88" t="n">
-        <v>0.0834967829299813</v>
+        <v>0.831201755923087</v>
       </c>
       <c r="G88"/>
       <c r="H88" t="n">
-        <v>1.73074764769325</v>
+        <v>0.369204862166525</v>
       </c>
       <c r="I88" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="89">
@@ -3062,25 +3054,23 @@
         <v>53</v>
       </c>
       <c r="B89" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C89" t="n">
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.191363321027034</v>
+        <v>-0.464681491897395</v>
       </c>
       <c r="E89" t="n">
-        <v>-1.46328235724133</v>
+        <v>-0.24304685362388</v>
       </c>
       <c r="F89" t="n">
-        <v>0.143390133292888</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.625163055985475</v>
-      </c>
+        <v>0.807969101477861</v>
+      </c>
+      <c r="G89"/>
       <c r="H89" t="n">
-        <v>1.46328235724133</v>
+        <v>0.24304685362388</v>
       </c>
       <c r="I89" t="s">
         <v>11</v>
@@ -3091,25 +3081,23 @@
         <v>53</v>
       </c>
       <c r="B90" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.146567277237516</v>
+        <v>-0.0182683792598074</v>
       </c>
       <c r="E90" t="n">
-        <v>-1.37581390411533</v>
+        <v>-0.127064915281692</v>
       </c>
       <c r="F90" t="n">
-        <v>0.168879255629964</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.662863555608717</v>
-      </c>
+        <v>0.898889019880745</v>
+      </c>
+      <c r="G90"/>
       <c r="H90" t="n">
-        <v>1.37581390411533</v>
+        <v>0.220082889127326</v>
       </c>
       <c r="I90" t="s">
         <v>11</v>
@@ -3120,23 +3108,25 @@
         <v>53</v>
       </c>
       <c r="B91" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.357747797379055</v>
+        <v>-0.0158910153931639</v>
       </c>
       <c r="E91" t="n">
-        <v>-1.26172621893209</v>
+        <v>-0.176388165960046</v>
       </c>
       <c r="F91" t="n">
-        <v>0.207047319046525</v>
-      </c>
-      <c r="G91"/>
+        <v>0.859989001102471</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.968466379060083</v>
+      </c>
       <c r="H91" t="n">
-        <v>1.26172621893209</v>
+        <v>0.176388165960046</v>
       </c>
       <c r="I91" t="s">
         <v>11</v>
@@ -3144,26 +3134,26 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D92" t="n">
-        <v>0.568852661112965</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E92" t="n">
-        <v>1.69911620492032</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0892972906656036</v>
+        <v>0.0651633670482164</v>
       </c>
       <c r="G92"/>
       <c r="H92" t="n">
-        <v>1.69911620492032</v>
+        <v>6.38827343899636</v>
       </c>
       <c r="I92" t="s">
         <v>13</v>
@@ -3171,28 +3161,28 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B93" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.127705649007195</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E93" t="n">
-        <v>-1.02792198997847</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F93" t="n">
-        <v>0.303986524655079</v>
+        <v>0.0279610507551714</v>
       </c>
       <c r="G93" t="n">
-        <v>0.763093745018922</v>
+        <v>0.334436097267736</v>
       </c>
       <c r="H93" t="n">
-        <v>1.4537012192891</v>
+        <v>4.39566482465688</v>
       </c>
       <c r="I93" t="s">
         <v>11</v>
@@ -3200,13 +3190,13 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B94" t="s">
         <v>27</v>
       </c>
       <c r="C94" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D94" t="n">
         <v>-0.449306074582525</v>
@@ -3219,7 +3209,7 @@
       </c>
       <c r="G94"/>
       <c r="H94" t="n">
-        <v>1.19236322199204</v>
+        <v>3.03994166811388</v>
       </c>
       <c r="I94" t="s">
         <v>11</v>
@@ -3227,26 +3217,28 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B95" t="s">
-        <v>57</v>
+        <v>25</v>
       </c>
       <c r="C95" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.141237121743142</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E95" t="n">
-        <v>-0.505075071717537</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F95" t="n">
-        <v>0.613506109324499</v>
-      </c>
-      <c r="G95"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H95" t="n">
-        <v>1.01015014343507</v>
+        <v>2.96189275053909</v>
       </c>
       <c r="I95" t="s">
         <v>11</v>
@@ -3254,109 +3246,111 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B96" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0728339894275881</v>
+        <v>-0.272696592226143</v>
       </c>
       <c r="E96" t="n">
-        <v>0.706727814492832</v>
+        <v>-1.27637770916738</v>
       </c>
       <c r="F96" t="n">
-        <v>0.47973564103236</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.870332217592113</v>
-      </c>
+        <v>0.201822032086846</v>
+      </c>
+      <c r="G96"/>
       <c r="H96" t="n">
-        <v>0.706727814492832</v>
+        <v>2.55275541833476</v>
       </c>
       <c r="I96" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B97" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>-0.0813258659038187</v>
+        <v>0.282847656074349</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.382914639728419</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="F97" t="n">
-        <v>0.701783056225352</v>
-      </c>
-      <c r="G97"/>
+        <v>0.0129523513132298</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.204334507786298</v>
+      </c>
       <c r="H97" t="n">
-        <v>0.382914639728419</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="I97" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B98" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0417765291221938</v>
+        <v>-0.140329115706343</v>
       </c>
       <c r="E98" t="n">
-        <v>0.213160526557962</v>
+        <v>-0.959469282447805</v>
       </c>
       <c r="F98" t="n">
-        <v>0.831201755923087</v>
-      </c>
-      <c r="G98"/>
+        <v>0.337322387113442</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.796124318021208</v>
+      </c>
       <c r="H98" t="n">
-        <v>0.369204862166525</v>
+        <v>2.14543853787624</v>
       </c>
       <c r="I98" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B99" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="C99" t="n">
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>-0.464681491897395</v>
+        <v>-1.30497438363151</v>
       </c>
       <c r="E99" t="n">
-        <v>-0.24304685362388</v>
+        <v>-2.07523837651259</v>
       </c>
       <c r="F99" t="n">
-        <v>0.807969101477861</v>
+        <v>0.0379644475275991</v>
       </c>
       <c r="G99"/>
       <c r="H99" t="n">
-        <v>0.24304685362388</v>
+        <v>2.07523837651259</v>
       </c>
       <c r="I99" t="s">
         <v>11</v>
@@ -3364,55 +3358,53 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="C100" t="n">
         <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>-0.0182683792598074</v>
+        <v>0.202760189088342</v>
       </c>
       <c r="E100" t="n">
-        <v>-0.127064915281692</v>
+        <v>1.0082954236419</v>
       </c>
       <c r="F100" t="n">
-        <v>0.898889019880745</v>
+        <v>0.31331265932097</v>
       </c>
       <c r="G100"/>
       <c r="H100" t="n">
-        <v>0.220082889127326</v>
+        <v>1.74641890278696</v>
       </c>
       <c r="I100" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B101" t="s">
-        <v>63</v>
+        <v>20</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.0158910153931639</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.176388165960046</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F101" t="n">
-        <v>0.859989001102471</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.968466379060083</v>
-      </c>
+        <v>0.390826854723006</v>
+      </c>
+      <c r="G101"/>
       <c r="H101" t="n">
-        <v>0.176388165960046</v>
+        <v>1.71623764545509</v>
       </c>
       <c r="I101" t="s">
         <v>11</v>
@@ -3420,55 +3412,57 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B102" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C102" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D102" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E102" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G102"/>
+        <v>0.0279610507551714</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.334436097267736</v>
+      </c>
       <c r="H102" t="n">
-        <v>6.38827343899636</v>
+        <v>5.81491798641822</v>
       </c>
       <c r="I102" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E103" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0362266370333839</v>
       </c>
       <c r="G103" t="n">
-        <v>0.334436097267736</v>
+        <v>0.381004286040762</v>
       </c>
       <c r="H103" t="n">
-        <v>4.39566482465688</v>
+        <v>4.68316363842221</v>
       </c>
       <c r="I103" t="s">
         <v>11</v>
@@ -3476,55 +3470,53 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B104" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C104" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D104" t="n">
-        <v>-0.449306074582525</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.843128119908009</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F104" t="n">
-        <v>0.39915679353664</v>
+        <v>0.0651633670482164</v>
       </c>
       <c r="G104"/>
       <c r="H104" t="n">
-        <v>3.03994166811388</v>
+        <v>4.51719146878823</v>
       </c>
       <c r="I104" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B105" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C105" t="n">
         <v>2</v>
       </c>
       <c r="D105" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G105"/>
       <c r="H105" t="n">
-        <v>2.96189275053909</v>
+        <v>3.34737288737526</v>
       </c>
       <c r="I105" t="s">
         <v>11</v>
@@ -3532,26 +3524,26 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B106" t="s">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="C106" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>-0.272696592226143</v>
+        <v>-1.30497438363151</v>
       </c>
       <c r="E106" t="n">
-        <v>-1.27637770916738</v>
+        <v>-2.07523837651259</v>
       </c>
       <c r="F106" t="n">
-        <v>0.201822032086846</v>
+        <v>0.0379644475275991</v>
       </c>
       <c r="G106"/>
       <c r="H106" t="n">
-        <v>2.55275541833476</v>
+        <v>2.93483025722123</v>
       </c>
       <c r="I106" t="s">
         <v>11</v>
@@ -3559,57 +3551,57 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
+        <v>63</v>
+      </c>
+      <c r="B107" t="s">
         <v>64</v>
       </c>
-      <c r="B107" t="s">
-        <v>12</v>
-      </c>
       <c r="C107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D107" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.350420430655839</v>
       </c>
       <c r="E107" t="n">
-        <v>2.48507673142061</v>
+        <v>-1.56791478927012</v>
       </c>
       <c r="F107" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.116901019836926</v>
       </c>
       <c r="G107" t="n">
-        <v>0.204334507786298</v>
+        <v>0.581593854164919</v>
       </c>
       <c r="H107" t="n">
-        <v>2.48507673142061</v>
+        <v>2.21736635963116</v>
       </c>
       <c r="I107" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B108" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="C108" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.140329115706343</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E108" t="n">
-        <v>-0.959469282447805</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F108" t="n">
-        <v>0.337322387113442</v>
+        <v>0.0527913184011619</v>
       </c>
       <c r="G108" t="n">
-        <v>0.796124318021208</v>
+        <v>0.435171678712281</v>
       </c>
       <c r="H108" t="n">
-        <v>2.14543853787624</v>
+        <v>1.93662402966198</v>
       </c>
       <c r="I108" t="s">
         <v>11</v>
@@ -3617,26 +3609,28 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B109" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>-1.30497438363151</v>
+        <v>-0.296782538842574</v>
       </c>
       <c r="E109" t="n">
-        <v>-2.07523837651259</v>
+        <v>-1.56768616274128</v>
       </c>
       <c r="F109" t="n">
-        <v>0.0379644475275991</v>
-      </c>
-      <c r="G109"/>
+        <v>0.116954392531525</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.581593854164919</v>
+      </c>
       <c r="H109" t="n">
-        <v>2.07523837651259</v>
+        <v>1.56768616274128</v>
       </c>
       <c r="I109" t="s">
         <v>11</v>
@@ -3644,53 +3638,55 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B110" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C110" t="n">
         <v>3</v>
       </c>
       <c r="D110" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E110" t="n">
-        <v>1.0082954236419</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F110" t="n">
-        <v>0.31331265932097</v>
+        <v>0.390826854723006</v>
       </c>
       <c r="G110"/>
       <c r="H110" t="n">
-        <v>1.74641890278696</v>
+        <v>1.4863053998953</v>
       </c>
       <c r="I110" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B111" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C111" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.170539952646192</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.03910409537338</v>
       </c>
       <c r="F111" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G111"/>
+        <v>0.298756326499217</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.762516147131893</v>
+      </c>
       <c r="H111" t="n">
-        <v>1.71623764545509</v>
+        <v>1.46951510439445</v>
       </c>
       <c r="I111" t="s">
         <v>11</v>
@@ -3698,13 +3694,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B112" t="s">
         <v>10</v>
       </c>
       <c r="C112" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D112" t="n">
         <v>-0.467382365575886</v>
@@ -3719,7 +3715,7 @@
         <v>0.334436097267736</v>
       </c>
       <c r="H112" t="n">
-        <v>5.81491798641822</v>
+        <v>6.9501563383002</v>
       </c>
       <c r="I112" t="s">
         <v>11</v>
@@ -3727,82 +3723,84 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B113" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D113" t="n">
-        <v>-0.531888018405323</v>
+        <v>0.282847656074349</v>
       </c>
       <c r="E113" t="n">
-        <v>-2.09437444905346</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.0129523513132298</v>
       </c>
       <c r="G113" t="n">
-        <v>0.381004286040762</v>
+        <v>0.204334507786298</v>
       </c>
       <c r="H113" t="n">
-        <v>4.68316363842221</v>
+        <v>4.3042791595277</v>
       </c>
       <c r="I113" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
+        <v>65</v>
+      </c>
+      <c r="B114" t="s">
         <v>66</v>
       </c>
-      <c r="B114" t="s">
-        <v>15</v>
-      </c>
       <c r="C114" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D114" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.582671827903238</v>
       </c>
       <c r="E114" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.73074764769325</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.0834967829299813</v>
       </c>
       <c r="G114"/>
       <c r="H114" t="n">
-        <v>4.51719146878823</v>
+        <v>2.99774286088503</v>
       </c>
       <c r="I114" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B115" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E115" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F115" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G115"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H115" t="n">
-        <v>3.34737288737526</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I115" t="s">
         <v>11</v>
@@ -3810,26 +3808,28 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B116" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C116" t="n">
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>-1.30497438363151</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E116" t="n">
-        <v>-2.07523837651259</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0379644475275991</v>
-      </c>
-      <c r="G116"/>
+        <v>0.0527913184011619</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.435171678712281</v>
+      </c>
       <c r="H116" t="n">
-        <v>2.93483025722123</v>
+        <v>2.73879996796561</v>
       </c>
       <c r="I116" t="s">
         <v>11</v>
@@ -3837,28 +3837,26 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B117" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.350420430655839</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E117" t="n">
-        <v>-1.56791478927012</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F117" t="n">
-        <v>0.116901019836926</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.390826854723006</v>
+      </c>
+      <c r="G117"/>
       <c r="H117" t="n">
-        <v>2.21736635963116</v>
+        <v>2.57435646818263</v>
       </c>
       <c r="I117" t="s">
         <v>11</v>
@@ -3866,28 +3864,26 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B118" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>-0.346644086928774</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E118" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G118" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G118"/>
       <c r="H118" t="n">
-        <v>1.93662402966198</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I118" t="s">
         <v>11</v>
@@ -3895,28 +3891,26 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B119" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C119" t="n">
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.296782538842574</v>
+        <v>-0.472120445097816</v>
       </c>
       <c r="E119" t="n">
-        <v>-1.56768616274128</v>
+        <v>-2.20017465442735</v>
       </c>
       <c r="F119" t="n">
-        <v>0.116954392531525</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.0277945058180277</v>
+      </c>
+      <c r="G119"/>
       <c r="H119" t="n">
-        <v>1.56768616274128</v>
+        <v>2.20017465442735</v>
       </c>
       <c r="I119" t="s">
         <v>11</v>
@@ -3924,26 +3918,28 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B120" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E120" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F120" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G120"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H120" t="n">
-        <v>1.4863053998953</v>
+        <v>2.09437444905346</v>
       </c>
       <c r="I120" t="s">
         <v>11</v>
@@ -3951,28 +3947,28 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B121" t="s">
-        <v>21</v>
+        <v>67</v>
       </c>
       <c r="C121" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.170539952646192</v>
+        <v>-0.24395134664857</v>
       </c>
       <c r="E121" t="n">
-        <v>-1.03910409537338</v>
+        <v>-2.08608978977804</v>
       </c>
       <c r="F121" t="n">
-        <v>0.298756326499217</v>
+        <v>0.0369704904012726</v>
       </c>
       <c r="G121" t="n">
-        <v>0.762516147131893</v>
+        <v>0.386605699624737</v>
       </c>
       <c r="H121" t="n">
-        <v>1.46951510439445</v>
+        <v>2.08608978977804</v>
       </c>
       <c r="I121" t="s">
         <v>11</v>
@@ -3986,7 +3982,7 @@
         <v>10</v>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D122" t="n">
         <v>-0.467382365575886</v>
@@ -4001,7 +3997,7 @@
         <v>0.334436097267736</v>
       </c>
       <c r="H122" t="n">
-        <v>6.9501563383002</v>
+        <v>6.59349723698531</v>
       </c>
       <c r="I122" t="s">
         <v>11</v>
@@ -4012,28 +4008,28 @@
         <v>68</v>
       </c>
       <c r="B123" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="C123" t="n">
         <v>3</v>
       </c>
       <c r="D123" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E123" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.0362266370333839</v>
       </c>
       <c r="G123" t="n">
-        <v>0.204334507786298</v>
+        <v>0.381004286040762</v>
       </c>
       <c r="H123" t="n">
-        <v>4.3042791595277</v>
+        <v>3.62756295583467</v>
       </c>
       <c r="I123" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="124">
@@ -4041,23 +4037,25 @@
         <v>68</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="C124" t="n">
         <v>3</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.582671827903238</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.73074764769325</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0834967829299813</v>
-      </c>
-      <c r="G124"/>
+        <v>0.0527913184011619</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.435171678712281</v>
+      </c>
       <c r="H124" t="n">
-        <v>2.99774286088503</v>
+        <v>3.35433121453333</v>
       </c>
       <c r="I124" t="s">
         <v>11</v>
@@ -4068,28 +4066,26 @@
         <v>68</v>
       </c>
       <c r="B125" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C125" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E125" t="n">
-        <v>-2.89999694915305</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F125" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G125" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G125"/>
       <c r="H125" t="n">
-        <v>2.89999694915305</v>
+        <v>3.19413671949818</v>
       </c>
       <c r="I125" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="126">
@@ -4097,25 +4093,23 @@
         <v>68</v>
       </c>
       <c r="B126" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C126" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>-0.346644086928774</v>
+        <v>-1.48587220752926</v>
       </c>
       <c r="E126" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.97618080518438</v>
       </c>
       <c r="F126" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G126" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.00291862733391663</v>
+      </c>
+      <c r="G126"/>
       <c r="H126" t="n">
-        <v>2.73879996796561</v>
+        <v>2.97618080518438</v>
       </c>
       <c r="I126" t="s">
         <v>11</v>
@@ -4126,23 +4120,25 @@
         <v>68</v>
       </c>
       <c r="B127" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C127" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.24395134664857</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.08608978977804</v>
       </c>
       <c r="F127" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G127"/>
+        <v>0.0369704904012726</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.386605699624737</v>
+      </c>
       <c r="H127" t="n">
-        <v>2.57435646818263</v>
+        <v>2.95017647303215</v>
       </c>
       <c r="I127" t="s">
         <v>11</v>
@@ -4153,23 +4149,23 @@
         <v>68</v>
       </c>
       <c r="B128" t="s">
-        <v>16</v>
+        <v>69</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D128" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.673259396707017</v>
       </c>
       <c r="E128" t="n">
-        <v>-2.36695006782304</v>
+        <v>-1.1698008416434</v>
       </c>
       <c r="F128" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.242081124896929</v>
       </c>
       <c r="G128"/>
       <c r="H128" t="n">
-        <v>2.36695006782304</v>
+        <v>2.86541516270464</v>
       </c>
       <c r="I128" t="s">
         <v>11</v>
@@ -4180,23 +4176,23 @@
         <v>68</v>
       </c>
       <c r="B129" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>-0.472120445097816</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E129" t="n">
-        <v>-2.20017465442735</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0277945058180277</v>
+        <v>0.0179353523795742</v>
       </c>
       <c r="G129"/>
       <c r="H129" t="n">
-        <v>2.20017465442735</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I129" t="s">
         <v>11</v>
@@ -4207,25 +4203,23 @@
         <v>68</v>
       </c>
       <c r="B130" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C130" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E130" t="n">
-        <v>-2.09437444905346</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F130" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G130" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.390826854723006</v>
+      </c>
+      <c r="G130"/>
       <c r="H130" t="n">
-        <v>2.09437444905346</v>
+        <v>2.1019532543603</v>
       </c>
       <c r="I130" t="s">
         <v>11</v>
@@ -4236,39 +4230,37 @@
         <v>68</v>
       </c>
       <c r="B131" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C131" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>-0.24395134664857</v>
+        <v>0.160200568560385</v>
       </c>
       <c r="E131" t="n">
-        <v>-2.08608978977804</v>
+        <v>0.973907884018594</v>
       </c>
       <c r="F131" t="n">
-        <v>0.0369704904012726</v>
-      </c>
-      <c r="G131" t="n">
-        <v>0.386605699624737</v>
-      </c>
+        <v>0.330102278801738</v>
+      </c>
+      <c r="G131"/>
       <c r="H131" t="n">
-        <v>2.08608978977804</v>
+        <v>1.94781576803719</v>
       </c>
       <c r="I131" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B132" t="s">
         <v>10</v>
       </c>
       <c r="C132" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D132" t="n">
         <v>-0.467382365575886</v>
@@ -4283,7 +4275,7 @@
         <v>0.334436097267736</v>
       </c>
       <c r="H132" t="n">
-        <v>6.59349723698531</v>
+        <v>8.22353588047989</v>
       </c>
       <c r="I132" t="s">
         <v>11</v>
@@ -4291,13 +4283,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B133" t="s">
         <v>25</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D133" t="n">
         <v>-0.531888018405323</v>
@@ -4312,7 +4304,7 @@
         <v>0.381004286040762</v>
       </c>
       <c r="H133" t="n">
-        <v>3.62756295583467</v>
+        <v>4.68316363842221</v>
       </c>
       <c r="I133" t="s">
         <v>11</v>
@@ -4320,82 +4312,82 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B134" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C134" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D134" t="n">
-        <v>-0.346644086928774</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E134" t="n">
-        <v>-1.93662402966198</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G134"/>
       <c r="H134" t="n">
-        <v>3.35433121453333</v>
+        <v>4.12361277337535</v>
       </c>
       <c r="I134" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B135" t="s">
-        <v>15</v>
+        <v>69</v>
       </c>
       <c r="C135" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D135" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.673259396707017</v>
       </c>
       <c r="E135" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.1698008416434</v>
       </c>
       <c r="F135" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.242081124896929</v>
       </c>
       <c r="G135"/>
       <c r="H135" t="n">
-        <v>3.19413671949818</v>
+        <v>3.50940252493021</v>
       </c>
       <c r="I135" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B136" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D136" t="n">
-        <v>-1.48587220752926</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E136" t="n">
-        <v>-2.97618080518438</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F136" t="n">
-        <v>0.00291862733391663</v>
-      </c>
-      <c r="G136"/>
+        <v>0.0527913184011619</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.435171678712281</v>
+      </c>
       <c r="H136" t="n">
-        <v>2.97618080518438</v>
+        <v>3.35433121453333</v>
       </c>
       <c r="I136" t="s">
         <v>11</v>
@@ -4403,28 +4395,26 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B137" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="C137" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.24395134664857</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E137" t="n">
-        <v>-2.08608978977804</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F137" t="n">
-        <v>0.0369704904012726</v>
-      </c>
-      <c r="G137" t="n">
-        <v>0.386605699624737</v>
-      </c>
+        <v>0.390826854723006</v>
+      </c>
+      <c r="G137"/>
       <c r="H137" t="n">
-        <v>2.95017647303215</v>
+        <v>2.97261079979059</v>
       </c>
       <c r="I137" t="s">
         <v>11</v>
@@ -4432,26 +4422,28 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B138" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="C138" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E138" t="n">
-        <v>-1.1698008416434</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F138" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G138"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H138" t="n">
-        <v>2.86541516270464</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I138" t="s">
         <v>11</v>
@@ -4459,26 +4451,28 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C139" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.191363321027034</v>
       </c>
       <c r="E139" t="n">
-        <v>-2.36695006782304</v>
+        <v>-1.46328235724133</v>
       </c>
       <c r="F139" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G139"/>
+        <v>0.143390133292888</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.625163055985475</v>
+      </c>
       <c r="H139" t="n">
-        <v>2.36695006782304</v>
+        <v>2.53447938856114</v>
       </c>
       <c r="I139" t="s">
         <v>11</v>
@@ -4486,26 +4480,26 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B140" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>-0.121791813728833</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E140" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F140" t="n">
-        <v>0.390826854723006</v>
+        <v>0.0179353523795742</v>
       </c>
       <c r="G140"/>
       <c r="H140" t="n">
-        <v>2.1019532543603</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I140" t="s">
         <v>11</v>
@@ -4513,40 +4507,40 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B141" t="s">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="C141" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D141" t="n">
-        <v>0.160200568560385</v>
+        <v>-0.449306074582525</v>
       </c>
       <c r="E141" t="n">
-        <v>0.973907884018594</v>
+        <v>-0.843128119908009</v>
       </c>
       <c r="F141" t="n">
-        <v>0.330102278801738</v>
+        <v>0.39915679353664</v>
       </c>
       <c r="G141"/>
       <c r="H141" t="n">
-        <v>1.94781576803719</v>
+        <v>2.06523368156673</v>
       </c>
       <c r="I141" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B142" t="s">
         <v>10</v>
       </c>
       <c r="C142" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D142" t="n">
         <v>-0.467382365575886</v>
@@ -4561,7 +4555,7 @@
         <v>0.334436097267736</v>
       </c>
       <c r="H142" t="n">
-        <v>8.22353588047989</v>
+        <v>7.28938546377511</v>
       </c>
       <c r="I142" t="s">
         <v>11</v>
@@ -4569,28 +4563,28 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B143" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C143" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E143" t="n">
-        <v>-2.09437444905346</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.0527913184011619</v>
       </c>
       <c r="G143" t="n">
-        <v>0.381004286040762</v>
+        <v>0.435171678712281</v>
       </c>
       <c r="H143" t="n">
-        <v>4.68316363842221</v>
+        <v>3.35433121453333</v>
       </c>
       <c r="I143" t="s">
         <v>11</v>
@@ -4598,40 +4592,42 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B144" t="s">
-        <v>15</v>
+        <v>32</v>
       </c>
       <c r="C144" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E144" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F144" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G144"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H144" t="n">
-        <v>4.12361277337535</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I144" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B145" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C145" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D145" t="n">
         <v>-0.673259396707017</v>
@@ -4644,7 +4640,7 @@
       </c>
       <c r="G145"/>
       <c r="H145" t="n">
-        <v>3.50940252493021</v>
+        <v>2.86541516270464</v>
       </c>
       <c r="I145" t="s">
         <v>11</v>
@@ -4652,28 +4648,26 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B146" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E146" t="n">
-        <v>-1.93662402966198</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F146" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G146" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.390826854723006</v>
+      </c>
+      <c r="G146"/>
       <c r="H146" t="n">
-        <v>3.35433121453333</v>
+        <v>2.84605816052876</v>
       </c>
       <c r="I146" t="s">
         <v>11</v>
@@ -4681,55 +4675,55 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B147" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C147" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>-0.121791813728833</v>
+        <v>0.282847656074349</v>
       </c>
       <c r="E147" t="n">
-        <v>-0.858118822727544</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="F147" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G147"/>
+        <v>0.0129523513132298</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0.204334507786298</v>
+      </c>
       <c r="H147" t="n">
-        <v>2.97261079979059</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="I147" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B148" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C148" t="n">
         <v>1</v>
       </c>
       <c r="D148" t="n">
-        <v>-0.359164820470093</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E148" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F148" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G148" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G148"/>
       <c r="H148" t="n">
-        <v>2.89999694915305</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I148" t="s">
         <v>11</v>
@@ -4737,28 +4731,26 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B149" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.191363321027034</v>
+        <v>-0.293068543126831</v>
       </c>
       <c r="E149" t="n">
-        <v>-1.46328235724133</v>
+        <v>-2.22467703206467</v>
       </c>
       <c r="F149" t="n">
-        <v>0.143390133292888</v>
-      </c>
-      <c r="G149" t="n">
-        <v>0.625163055985475</v>
-      </c>
+        <v>0.0261029272182321</v>
+      </c>
+      <c r="G149"/>
       <c r="H149" t="n">
-        <v>2.53447938856114</v>
+        <v>2.22467703206467</v>
       </c>
       <c r="I149" t="s">
         <v>11</v>
@@ -4766,26 +4758,28 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C150" t="n">
         <v>1</v>
       </c>
       <c r="D150" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E150" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G150"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H150" t="n">
-        <v>2.36695006782304</v>
+        <v>2.09437444905346</v>
       </c>
       <c r="I150" t="s">
         <v>11</v>
@@ -4793,26 +4787,28 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B151" t="s">
-        <v>27</v>
+        <v>67</v>
       </c>
       <c r="C151" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.24395134664857</v>
       </c>
       <c r="E151" t="n">
-        <v>-0.843128119908009</v>
+        <v>-2.08608978977804</v>
       </c>
       <c r="F151" t="n">
-        <v>0.39915679353664</v>
-      </c>
-      <c r="G151"/>
+        <v>0.0369704904012726</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0.386605699624737</v>
+      </c>
       <c r="H151" t="n">
-        <v>2.06523368156673</v>
+        <v>2.08608978977804</v>
       </c>
       <c r="I151" t="s">
         <v>11</v>
@@ -4820,28 +4816,26 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D152" t="n">
-        <v>-0.467382365575886</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G152" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G152"/>
       <c r="H152" t="n">
-        <v>7.28938546377511</v>
+        <v>4.73390013564608</v>
       </c>
       <c r="I152" t="s">
         <v>11</v>
@@ -4849,28 +4843,26 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B153" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C153" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.293068543126831</v>
       </c>
       <c r="E153" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.22467703206467</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G153" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0261029272182321</v>
+      </c>
+      <c r="G153"/>
       <c r="H153" t="n">
-        <v>3.35433121453333</v>
+        <v>4.44935406412935</v>
       </c>
       <c r="I153" t="s">
         <v>11</v>
@@ -4878,55 +4870,55 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B154" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.282847656074349</v>
       </c>
       <c r="E154" t="n">
-        <v>-2.89999694915305</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="F154" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0129523513132298</v>
       </c>
       <c r="G154" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.204334507786298</v>
       </c>
       <c r="H154" t="n">
-        <v>2.89999694915305</v>
+        <v>4.3042791595277</v>
       </c>
       <c r="I154" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B155" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C155" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.472120445097816</v>
       </c>
       <c r="E155" t="n">
-        <v>-1.1698008416434</v>
+        <v>-2.20017465442735</v>
       </c>
       <c r="F155" t="n">
-        <v>0.242081124896929</v>
+        <v>0.0277945058180277</v>
       </c>
       <c r="G155"/>
       <c r="H155" t="n">
-        <v>2.86541516270464</v>
+        <v>3.1115168358807</v>
       </c>
       <c r="I155" t="s">
         <v>11</v>
@@ -4934,26 +4926,28 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B156" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C156" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F156" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G156"/>
+        <v>0.0279610507551714</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0.334436097267736</v>
+      </c>
       <c r="H156" t="n">
-        <v>2.84605816052876</v>
+        <v>3.10820440533805</v>
       </c>
       <c r="I156" t="s">
         <v>11</v>
@@ -4961,28 +4955,26 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B157" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="C157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D157" t="n">
-        <v>0.282847656074349</v>
+        <v>0.519825670239084</v>
       </c>
       <c r="E157" t="n">
-        <v>2.48507673142061</v>
+        <v>2.1468751925701</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G157" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.0318032190620896</v>
+      </c>
+      <c r="G157"/>
       <c r="H157" t="n">
-        <v>2.48507673142061</v>
+        <v>3.03614001405499</v>
       </c>
       <c r="I157" t="s">
         <v>13</v>
@@ -4990,53 +4982,55 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B158" t="s">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C158" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D158" t="n">
-        <v>-1.38550615703734</v>
+        <v>0.568852661112965</v>
       </c>
       <c r="E158" t="n">
-        <v>-2.36695006782304</v>
+        <v>1.69911620492032</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0892972906656036</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="n">
-        <v>2.36695006782304</v>
+        <v>2.94295559488561</v>
       </c>
       <c r="I158" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B159" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.293068543126831</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.22467703206467</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F159" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G159"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H159" t="n">
-        <v>2.22467703206467</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I159" t="s">
         <v>11</v>
@@ -5044,84 +5038,82 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B160" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C160" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D160" t="n">
-        <v>-0.531888018405323</v>
+        <v>0.202760189088342</v>
       </c>
       <c r="E160" t="n">
-        <v>-2.09437444905346</v>
+        <v>1.0082954236419</v>
       </c>
       <c r="F160" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G160" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.31331265932097</v>
+      </c>
+      <c r="G160"/>
       <c r="H160" t="n">
-        <v>2.09437444905346</v>
+        <v>2.667698939041</v>
       </c>
       <c r="I160" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B161" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="C161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D161" t="n">
-        <v>-0.24395134664857</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E161" t="n">
-        <v>-2.08608978977804</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0369704904012726</v>
-      </c>
-      <c r="G161" t="n">
-        <v>0.386605699624737</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G161"/>
       <c r="H161" t="n">
-        <v>2.08608978977804</v>
+        <v>2.60800171048597</v>
       </c>
       <c r="I161" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B162" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D162" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E162" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F162" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G162"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H162" t="n">
-        <v>4.73390013564608</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I162" t="s">
         <v>11</v>
@@ -5129,55 +5121,53 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B163" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D163" t="n">
-        <v>-0.293068543126831</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E163" t="n">
-        <v>-2.22467703206467</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0261029272182321</v>
+        <v>0.0651633670482164</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="n">
-        <v>4.44935406412935</v>
+        <v>2.60800171048597</v>
       </c>
       <c r="I163" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B164" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C164" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0.282847656074349</v>
+        <v>0.384791636175517</v>
       </c>
       <c r="E164" t="n">
-        <v>2.48507673142061</v>
+        <v>2.30101784326713</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G164" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.0213906225293496</v>
+      </c>
+      <c r="G164"/>
       <c r="H164" t="n">
-        <v>4.3042791595277</v>
+        <v>2.30101784326713</v>
       </c>
       <c r="I164" t="s">
         <v>13</v>
@@ -5185,26 +5175,28 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B165" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E165" t="n">
-        <v>-2.20017465442735</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G165"/>
+        <v>0.0279610507551714</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0.334436097267736</v>
+      </c>
       <c r="H165" t="n">
-        <v>3.1115168358807</v>
+        <v>2.19783241232844</v>
       </c>
       <c r="I165" t="s">
         <v>11</v>
@@ -5212,28 +5204,28 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B166" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C166" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.235951201675001</v>
       </c>
       <c r="E166" t="n">
-        <v>-2.19783241232844</v>
+        <v>-1.80370004209605</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0712783429559855</v>
       </c>
       <c r="G166" t="n">
-        <v>0.334436097267736</v>
+        <v>0.503626901967002</v>
       </c>
       <c r="H166" t="n">
-        <v>3.10820440533805</v>
+        <v>1.80370004209605</v>
       </c>
       <c r="I166" t="s">
         <v>11</v>
@@ -5241,139 +5233,139 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="C167" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D167" t="n">
-        <v>0.519825670239084</v>
+        <v>-0.272696592226143</v>
       </c>
       <c r="E167" t="n">
-        <v>2.1468751925701</v>
+        <v>-1.27637770916738</v>
       </c>
       <c r="F167" t="n">
-        <v>0.0318032190620896</v>
+        <v>0.201822032086846</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="n">
-        <v>3.03614001405499</v>
+        <v>1.27637770916738</v>
       </c>
       <c r="I167" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B168" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>0.568852661112965</v>
+        <v>-0.127705649007195</v>
       </c>
       <c r="E168" t="n">
-        <v>1.69911620492032</v>
+        <v>-1.02792198997847</v>
       </c>
       <c r="F168" t="n">
-        <v>0.0892972906656036</v>
-      </c>
-      <c r="G168"/>
+        <v>0.303986524655079</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0.763093745018922</v>
+      </c>
       <c r="H168" t="n">
-        <v>2.94295559488561</v>
+        <v>1.02792198997847</v>
       </c>
       <c r="I168" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
+        <v>74</v>
+      </c>
+      <c r="B169" t="s">
         <v>75</v>
       </c>
-      <c r="B169" t="s">
-        <v>32</v>
-      </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.175437982401927</v>
       </c>
       <c r="E169" t="n">
-        <v>-2.89999694915305</v>
+        <v>1.02118050571171</v>
       </c>
       <c r="F169" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G169" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.307168926567477</v>
+      </c>
+      <c r="G169"/>
       <c r="H169" t="n">
-        <v>2.89999694915305</v>
+        <v>1.02118050571171</v>
       </c>
       <c r="I169" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B170" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E170" t="n">
-        <v>1.0082954236419</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F170" t="n">
-        <v>0.31331265932097</v>
+        <v>0.390826854723006</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="n">
-        <v>2.667698939041</v>
+        <v>0.858118822727544</v>
       </c>
       <c r="I170" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B171" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="C171" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D171" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.449306074582525</v>
       </c>
       <c r="E171" t="n">
-        <v>1.84413569483074</v>
+        <v>-0.843128119908009</v>
       </c>
       <c r="F171" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.39915679353664</v>
       </c>
       <c r="G171"/>
       <c r="H171" t="n">
-        <v>2.60800171048597</v>
+        <v>0.843128119908009</v>
       </c>
       <c r="I171" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="172">
@@ -5381,25 +5373,23 @@
         <v>76</v>
       </c>
       <c r="B172" t="s">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="C172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.293068543126831</v>
       </c>
       <c r="E172" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.22467703206467</v>
       </c>
       <c r="F172" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G172" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0261029272182321</v>
+      </c>
+      <c r="G172"/>
       <c r="H172" t="n">
-        <v>2.89999694915305</v>
+        <v>3.14616843064579</v>
       </c>
       <c r="I172" t="s">
         <v>11</v>
@@ -5410,26 +5400,28 @@
         <v>76</v>
       </c>
       <c r="B173" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C173" t="n">
         <v>2</v>
       </c>
       <c r="D173" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E173" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G173"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H173" t="n">
-        <v>2.60800171048597</v>
+        <v>2.96189275053909</v>
       </c>
       <c r="I173" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="174">
@@ -5437,23 +5429,23 @@
         <v>76</v>
       </c>
       <c r="B174" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="C174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D174" t="n">
-        <v>0.384791636175517</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E174" t="n">
-        <v>2.30101784326713</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0213906225293496</v>
+        <v>0.0651633670482164</v>
       </c>
       <c r="G174"/>
       <c r="H174" t="n">
-        <v>2.30101784326713</v>
+        <v>2.60800171048597</v>
       </c>
       <c r="I174" t="s">
         <v>13</v>
@@ -5464,25 +5456,23 @@
         <v>76</v>
       </c>
       <c r="B175" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C175" t="n">
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>-0.467382365575886</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E175" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G175" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G175"/>
       <c r="H175" t="n">
-        <v>2.19783241232844</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I175" t="s">
         <v>11</v>
@@ -5493,25 +5483,23 @@
         <v>76</v>
       </c>
       <c r="B176" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.235951201675001</v>
+        <v>-0.472120445097816</v>
       </c>
       <c r="E176" t="n">
-        <v>-1.80370004209605</v>
+        <v>-2.20017465442735</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0712783429559855</v>
-      </c>
-      <c r="G176" t="n">
-        <v>0.503626901967002</v>
-      </c>
+        <v>0.0277945058180277</v>
+      </c>
+      <c r="G176"/>
       <c r="H176" t="n">
-        <v>1.80370004209605</v>
+        <v>2.20017465442735</v>
       </c>
       <c r="I176" t="s">
         <v>11</v>
@@ -5522,23 +5510,23 @@
         <v>76</v>
       </c>
       <c r="B177" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>-0.272696592226143</v>
+        <v>-1.0424996815487</v>
       </c>
       <c r="E177" t="n">
-        <v>-1.27637770916738</v>
+        <v>-2.19286854490787</v>
       </c>
       <c r="F177" t="n">
-        <v>0.201822032086846</v>
+        <v>0.0283168515981792</v>
       </c>
       <c r="G177"/>
       <c r="H177" t="n">
-        <v>1.27637770916738</v>
+        <v>2.19286854490787</v>
       </c>
       <c r="I177" t="s">
         <v>11</v>
@@ -5549,25 +5537,25 @@
         <v>76</v>
       </c>
       <c r="B178" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="C178" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.127705649007195</v>
+        <v>-0.170539952646192</v>
       </c>
       <c r="E178" t="n">
-        <v>-1.02792198997847</v>
+        <v>-1.03910409537338</v>
       </c>
       <c r="F178" t="n">
-        <v>0.303986524655079</v>
+        <v>0.298756326499217</v>
       </c>
       <c r="G178" t="n">
-        <v>0.763093745018922</v>
+        <v>0.762516147131893</v>
       </c>
       <c r="H178" t="n">
-        <v>1.02792198997847</v>
+        <v>1.79978108753958</v>
       </c>
       <c r="I178" t="s">
         <v>11</v>
@@ -5578,23 +5566,23 @@
         <v>76</v>
       </c>
       <c r="B179" t="s">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="C179" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D179" t="n">
-        <v>0.175437982401927</v>
+        <v>0.202760189088342</v>
       </c>
       <c r="E179" t="n">
-        <v>1.02118050571171</v>
+        <v>1.0082954236419</v>
       </c>
       <c r="F179" t="n">
-        <v>0.307168926567477</v>
+        <v>0.31331265932097</v>
       </c>
       <c r="G179"/>
       <c r="H179" t="n">
-        <v>1.02118050571171</v>
+        <v>1.74641890278696</v>
       </c>
       <c r="I179" t="s">
         <v>13</v>
@@ -5605,23 +5593,23 @@
         <v>76</v>
       </c>
       <c r="B180" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.673259396707017</v>
       </c>
       <c r="E180" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.1698008416434</v>
       </c>
       <c r="F180" t="n">
-        <v>0.390826854723006</v>
+        <v>0.242081124896929</v>
       </c>
       <c r="G180"/>
       <c r="H180" t="n">
-        <v>0.858118822727544</v>
+        <v>1.65434821552756</v>
       </c>
       <c r="I180" t="s">
         <v>11</v>
@@ -5632,23 +5620,25 @@
         <v>76</v>
       </c>
       <c r="B181" t="s">
-        <v>27</v>
+        <v>64</v>
       </c>
       <c r="C181" t="n">
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.350420430655839</v>
       </c>
       <c r="E181" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.56791478927012</v>
       </c>
       <c r="F181" t="n">
-        <v>0.39915679353664</v>
-      </c>
-      <c r="G181"/>
+        <v>0.116901019836926</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0.581593854164919</v>
+      </c>
       <c r="H181" t="n">
-        <v>0.843128119908009</v>
+        <v>1.56791478927012</v>
       </c>
       <c r="I181" t="s">
         <v>11</v>
@@ -5656,26 +5646,28 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B182" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.293068543126831</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E182" t="n">
-        <v>-2.22467703206467</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F182" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G182"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H182" t="n">
-        <v>3.14616843064579</v>
+        <v>2.89999694915305</v>
       </c>
       <c r="I182" t="s">
         <v>11</v>
@@ -5683,28 +5675,26 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B183" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D183" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E183" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G183" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.0179353523795742</v>
+      </c>
+      <c r="G183"/>
       <c r="H183" t="n">
-        <v>2.96189275053909</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I183" t="s">
         <v>11</v>
@@ -5712,107 +5702,109 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B184" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D184" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E184" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G184"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H184" t="n">
-        <v>2.60800171048597</v>
+        <v>2.09437444905346</v>
       </c>
       <c r="I184" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B185" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
       </c>
       <c r="D185" t="n">
-        <v>-1.38550615703734</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E185" t="n">
-        <v>-2.36695006782304</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0651633670482164</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="n">
-        <v>2.36695006782304</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="I185" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B186" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C186" t="n">
         <v>1</v>
       </c>
       <c r="D186" t="n">
-        <v>-0.472120445097816</v>
+        <v>0.568852661112965</v>
       </c>
       <c r="E186" t="n">
-        <v>-2.20017465442735</v>
+        <v>1.69911620492032</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0277945058180277</v>
+        <v>0.0892972906656036</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="n">
-        <v>2.20017465442735</v>
+        <v>1.69911620492032</v>
       </c>
       <c r="I186" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B187" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>-1.0424996815487</v>
+        <v>-0.449306074582525</v>
       </c>
       <c r="E187" t="n">
-        <v>-2.19286854490787</v>
+        <v>-0.843128119908009</v>
       </c>
       <c r="F187" t="n">
-        <v>0.0283168515981792</v>
+        <v>0.39915679353664</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="n">
-        <v>2.19286854490787</v>
+        <v>1.68625623981602</v>
       </c>
       <c r="I187" t="s">
         <v>11</v>
@@ -5820,28 +5812,28 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
+        <v>77</v>
+      </c>
+      <c r="B188" t="s">
         <v>78</v>
       </c>
-      <c r="B188" t="s">
-        <v>21</v>
-      </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.170539952646192</v>
+        <v>-0.3132774213401</v>
       </c>
       <c r="E188" t="n">
-        <v>-1.03910409537338</v>
+        <v>-1.21248994342222</v>
       </c>
       <c r="F188" t="n">
-        <v>0.298756326499217</v>
+        <v>0.225324889860883</v>
       </c>
       <c r="G188" t="n">
-        <v>0.762516147131893</v>
+        <v>0.702460900247728</v>
       </c>
       <c r="H188" t="n">
-        <v>1.79978108753958</v>
+        <v>1.21248994342222</v>
       </c>
       <c r="I188" t="s">
         <v>11</v>
@@ -5849,53 +5841,55 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B189" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C189" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.189243113934208</v>
       </c>
       <c r="E189" t="n">
-        <v>1.0082954236419</v>
+        <v>-1.06988637864807</v>
       </c>
       <c r="F189" t="n">
-        <v>0.31331265932097</v>
+        <v>0.284670455048985</v>
       </c>
       <c r="G189"/>
       <c r="H189" t="n">
-        <v>1.74641890278696</v>
+        <v>1.06988637864807</v>
       </c>
       <c r="I189" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B190" t="s">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="C190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.214989848836869</v>
       </c>
       <c r="E190" t="n">
-        <v>-1.1698008416434</v>
+        <v>-1.05077682479031</v>
       </c>
       <c r="F190" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G190"/>
+        <v>0.293361102116757</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0.758446085972238</v>
+      </c>
       <c r="H190" t="n">
-        <v>1.65434821552756</v>
+        <v>1.05077682479031</v>
       </c>
       <c r="I190" t="s">
         <v>11</v>
@@ -5903,28 +5897,26 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B191" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.350420430655839</v>
+        <v>-0.141237121743142</v>
       </c>
       <c r="E191" t="n">
-        <v>-1.56791478927012</v>
+        <v>-0.505075071717537</v>
       </c>
       <c r="F191" t="n">
-        <v>0.116901019836926</v>
-      </c>
-      <c r="G191" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.613506109324499</v>
+      </c>
+      <c r="G191"/>
       <c r="H191" t="n">
-        <v>1.56791478927012</v>
+        <v>1.01015014343507</v>
       </c>
       <c r="I191" t="s">
         <v>11</v>
@@ -5935,28 +5927,26 @@
         <v>79</v>
       </c>
       <c r="B192" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D192" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E192" t="n">
-        <v>-2.89999694915305</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F192" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G192" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G192"/>
       <c r="H192" t="n">
-        <v>2.89999694915305</v>
+        <v>3.19413671949818</v>
       </c>
       <c r="I192" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="193">
@@ -5964,23 +5954,23 @@
         <v>79</v>
       </c>
       <c r="B193" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.472120445097816</v>
       </c>
       <c r="E193" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.20017465442735</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0277945058180277</v>
       </c>
       <c r="G193"/>
       <c r="H193" t="n">
-        <v>2.36695006782304</v>
+        <v>3.1115168358807</v>
       </c>
       <c r="I193" t="s">
         <v>11</v>
@@ -5994,7 +5984,7 @@
         <v>25</v>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D194" t="n">
         <v>-0.531888018405323</v>
@@ -6009,7 +5999,7 @@
         <v>0.381004286040762</v>
       </c>
       <c r="H194" t="n">
-        <v>2.09437444905346</v>
+        <v>2.96189275053909</v>
       </c>
       <c r="I194" t="s">
         <v>11</v>
@@ -6020,26 +6010,26 @@
         <v>79</v>
       </c>
       <c r="B195" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C195" t="n">
         <v>1</v>
       </c>
       <c r="D195" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.293068543126831</v>
       </c>
       <c r="E195" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.22467703206467</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.0261029272182321</v>
       </c>
       <c r="G195"/>
       <c r="H195" t="n">
-        <v>1.84413569483074</v>
+        <v>2.22467703206467</v>
       </c>
       <c r="I195" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="196">
@@ -6047,26 +6037,28 @@
         <v>79</v>
       </c>
       <c r="B196" t="s">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>0.568852661112965</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E196" t="n">
-        <v>1.69911620492032</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0892972906656036</v>
-      </c>
-      <c r="G196"/>
+        <v>0.0279610507551714</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0.334436097267736</v>
+      </c>
       <c r="H196" t="n">
-        <v>1.69911620492032</v>
+        <v>2.19783241232844</v>
       </c>
       <c r="I196" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="197">
@@ -6074,23 +6066,23 @@
         <v>79</v>
       </c>
       <c r="B197" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C197" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.204529625385548</v>
       </c>
       <c r="E197" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.10017496528803</v>
       </c>
       <c r="F197" t="n">
-        <v>0.39915679353664</v>
+        <v>0.271255896090862</v>
       </c>
       <c r="G197"/>
       <c r="H197" t="n">
-        <v>1.68625623981602</v>
+        <v>1.55588235689368</v>
       </c>
       <c r="I197" t="s">
         <v>11</v>
@@ -6101,28 +6093,26 @@
         <v>79</v>
       </c>
       <c r="B198" t="s">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D198" t="n">
-        <v>-0.3132774213401</v>
+        <v>0.202760189088342</v>
       </c>
       <c r="E198" t="n">
-        <v>-1.21248994342222</v>
+        <v>1.0082954236419</v>
       </c>
       <c r="F198" t="n">
-        <v>0.225324889860883</v>
-      </c>
-      <c r="G198" t="n">
-        <v>0.702460900247728</v>
-      </c>
+        <v>0.31331265932097</v>
+      </c>
+      <c r="G198"/>
       <c r="H198" t="n">
-        <v>1.21248994342222</v>
+        <v>1.42594506299311</v>
       </c>
       <c r="I198" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="199">
@@ -6130,23 +6120,23 @@
         <v>79</v>
       </c>
       <c r="B199" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.189243113934208</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E199" t="n">
-        <v>-1.06988637864807</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F199" t="n">
-        <v>0.284670455048985</v>
+        <v>0.390826854723006</v>
       </c>
       <c r="G199"/>
       <c r="H199" t="n">
-        <v>1.06988637864807</v>
+        <v>1.21356327722893</v>
       </c>
       <c r="I199" t="s">
         <v>11</v>
@@ -6157,25 +6147,25 @@
         <v>79</v>
       </c>
       <c r="B200" t="s">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.214989848836869</v>
+        <v>-0.3132774213401</v>
       </c>
       <c r="E200" t="n">
-        <v>-1.05077682479031</v>
+        <v>-1.21248994342222</v>
       </c>
       <c r="F200" t="n">
-        <v>0.293361102116757</v>
+        <v>0.225324889860883</v>
       </c>
       <c r="G200" t="n">
-        <v>0.758446085972238</v>
+        <v>0.702460900247728</v>
       </c>
       <c r="H200" t="n">
-        <v>1.05077682479031</v>
+        <v>1.21248994342222</v>
       </c>
       <c r="I200" t="s">
         <v>11</v>
@@ -6186,23 +6176,23 @@
         <v>79</v>
       </c>
       <c r="B201" t="s">
-        <v>57</v>
+        <v>81</v>
       </c>
       <c r="C201" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.141237121743142</v>
+        <v>-0.229813761004121</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.505075071717537</v>
+        <v>-0.856734680465064</v>
       </c>
       <c r="F201" t="n">
-        <v>0.613506109324499</v>
+        <v>0.391591532264627</v>
       </c>
       <c r="G201"/>
       <c r="H201" t="n">
-        <v>1.01015014343507</v>
+        <v>1.21160580446907</v>
       </c>
       <c r="I201" t="s">
         <v>11</v>
@@ -6210,53 +6200,57 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B202" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C202" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D202" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E202" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G202"/>
+        <v>0.0279610507551714</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0.334436097267736</v>
+      </c>
       <c r="H202" t="n">
-        <v>3.19413671949818</v>
+        <v>9.58012938017788</v>
       </c>
       <c r="I202" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B203" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C203" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E203" t="n">
-        <v>-2.20017465442735</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F203" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G203"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H203" t="n">
-        <v>3.1115168358807</v>
+        <v>6.28312334716039</v>
       </c>
       <c r="I203" t="s">
         <v>11</v>
@@ -6264,55 +6258,53 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B204" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C204" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D204" t="n">
-        <v>-0.531888018405323</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E204" t="n">
-        <v>-2.09437444905346</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G204" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G204"/>
       <c r="H204" t="n">
-        <v>2.96189275053909</v>
+        <v>5.21600342097193</v>
       </c>
       <c r="I204" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B205" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>-0.293068543126831</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E205" t="n">
-        <v>-2.22467703206467</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0261029272182321</v>
+        <v>0.0179353523795742</v>
       </c>
       <c r="G205"/>
       <c r="H205" t="n">
-        <v>2.22467703206467</v>
+        <v>4.73390013564608</v>
       </c>
       <c r="I205" t="s">
         <v>11</v>
@@ -6320,28 +6312,28 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B206" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C206" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.346644086928774</v>
       </c>
       <c r="E206" t="n">
-        <v>-2.19783241232844</v>
+        <v>-1.93662402966198</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0527913184011619</v>
       </c>
       <c r="G206" t="n">
-        <v>0.334436097267736</v>
+        <v>0.435171678712281</v>
       </c>
       <c r="H206" t="n">
-        <v>2.19783241232844</v>
+        <v>4.33042297718376</v>
       </c>
       <c r="I206" t="s">
         <v>11</v>
@@ -6349,26 +6341,28 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B207" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="C207" t="n">
         <v>2</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.204529625385548</v>
+        <v>-0.359164820470093</v>
       </c>
       <c r="E207" t="n">
-        <v>-1.10017496528803</v>
+        <v>-2.89999694915305</v>
       </c>
       <c r="F207" t="n">
-        <v>0.271255896090862</v>
-      </c>
-      <c r="G207"/>
+        <v>0.00373166292145953</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0.0973432101530153</v>
+      </c>
       <c r="H207" t="n">
-        <v>1.55588235689368</v>
+        <v>4.10121501633284</v>
       </c>
       <c r="I207" t="s">
         <v>11</v>
@@ -6376,53 +6370,53 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B208" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C208" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D208" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.121791813728833</v>
       </c>
       <c r="E208" t="n">
-        <v>1.0082954236419</v>
+        <v>-0.858118822727544</v>
       </c>
       <c r="F208" t="n">
-        <v>0.31331265932097</v>
+        <v>0.390826854723006</v>
       </c>
       <c r="G208"/>
       <c r="H208" t="n">
-        <v>1.42594506299311</v>
+        <v>4.0249340499224</v>
       </c>
       <c r="I208" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B209" t="s">
-        <v>20</v>
+        <v>69</v>
       </c>
       <c r="C209" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.673259396707017</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.1698008416434</v>
       </c>
       <c r="F209" t="n">
-        <v>0.390826854723006</v>
+        <v>0.242081124896929</v>
       </c>
       <c r="G209"/>
       <c r="H209" t="n">
-        <v>1.21356327722893</v>
+        <v>3.09500211046249</v>
       </c>
       <c r="I209" t="s">
         <v>11</v>
@@ -6430,28 +6424,28 @@
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B210" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.3132774213401</v>
+        <v>-0.244200454612073</v>
       </c>
       <c r="E210" t="n">
-        <v>-1.21248994342222</v>
+        <v>-1.16606476126988</v>
       </c>
       <c r="F210" t="n">
-        <v>0.225324889860883</v>
+        <v>0.243588262731164</v>
       </c>
       <c r="G210" t="n">
-        <v>0.702460900247728</v>
+        <v>0.721615526598251</v>
       </c>
       <c r="H210" t="n">
-        <v>1.21248994342222</v>
+        <v>2.60740007236651</v>
       </c>
       <c r="I210" t="s">
         <v>11</v>
@@ -6459,26 +6453,28 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B211" t="s">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="C211" t="n">
         <v>2</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.229813761004121</v>
+        <v>-0.235951201675001</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.856734680465064</v>
+        <v>-1.80370004209605</v>
       </c>
       <c r="F211" t="n">
-        <v>0.391591532264627</v>
-      </c>
-      <c r="G211"/>
+        <v>0.0712783429559855</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0.503626901967002</v>
+      </c>
       <c r="H211" t="n">
-        <v>1.21160580446907</v>
+        <v>2.55081706198515</v>
       </c>
       <c r="I211" t="s">
         <v>11</v>
@@ -6489,28 +6485,26 @@
         <v>84</v>
       </c>
       <c r="B212" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C212" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D212" t="n">
-        <v>-0.467382365575886</v>
+        <v>0.389552017255811</v>
       </c>
       <c r="E212" t="n">
-        <v>-2.19783241232844</v>
+        <v>1.84413569483074</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G212" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.0651633670482164</v>
+      </c>
+      <c r="G212"/>
       <c r="H212" t="n">
-        <v>9.58012938017788</v>
+        <v>4.51719146878823</v>
       </c>
       <c r="I212" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="213">
@@ -6518,28 +6512,26 @@
         <v>84</v>
       </c>
       <c r="B213" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C213" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D213" t="n">
-        <v>-0.531888018405323</v>
+        <v>0.519825670239084</v>
       </c>
       <c r="E213" t="n">
-        <v>-2.09437444905346</v>
+        <v>2.1468751925701</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G213" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.0318032190620896</v>
+      </c>
+      <c r="G213"/>
       <c r="H213" t="n">
-        <v>6.28312334716039</v>
+        <v>4.29375038514021</v>
       </c>
       <c r="I213" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="214">
@@ -6547,26 +6539,28 @@
         <v>84</v>
       </c>
       <c r="B214" t="s">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="C214" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D214" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.531888018405323</v>
       </c>
       <c r="E214" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.09437444905346</v>
       </c>
       <c r="F214" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G214"/>
+        <v>0.0362266370333839</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0.381004286040762</v>
+      </c>
       <c r="H214" t="n">
-        <v>5.21600342097193</v>
+        <v>4.18874889810692</v>
       </c>
       <c r="I214" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="215">
@@ -6574,23 +6568,23 @@
         <v>84</v>
       </c>
       <c r="B215" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C215" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D215" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.472120445097816</v>
       </c>
       <c r="E215" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.20017465442735</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0277945058180277</v>
       </c>
       <c r="G215"/>
       <c r="H215" t="n">
-        <v>4.73390013564608</v>
+        <v>3.81081428699347</v>
       </c>
       <c r="I215" t="s">
         <v>11</v>
@@ -6601,25 +6595,23 @@
         <v>84</v>
       </c>
       <c r="B216" t="s">
-        <v>19</v>
+        <v>66</v>
       </c>
       <c r="C216" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.582671827903238</v>
       </c>
       <c r="E216" t="n">
-        <v>-1.93662402966198</v>
+        <v>-1.73074764769325</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G216" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0834967829299813</v>
+      </c>
+      <c r="G216"/>
       <c r="H216" t="n">
-        <v>4.33042297718376</v>
+        <v>2.99774286088503</v>
       </c>
       <c r="I216" t="s">
         <v>11</v>
@@ -6630,28 +6622,28 @@
         <v>84</v>
       </c>
       <c r="B217" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D217" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.282847656074349</v>
       </c>
       <c r="E217" t="n">
-        <v>-2.89999694915305</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="F217" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0129523513132298</v>
       </c>
       <c r="G217" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.204334507786298</v>
       </c>
       <c r="H217" t="n">
-        <v>4.10121501633284</v>
+        <v>2.48507673142061</v>
       </c>
       <c r="I217" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218">
@@ -6659,26 +6651,26 @@
         <v>84</v>
       </c>
       <c r="B218" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="C218" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D218" t="n">
-        <v>-0.121791813728833</v>
+        <v>0.202760189088342</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.858118822727544</v>
+        <v>1.0082954236419</v>
       </c>
       <c r="F218" t="n">
-        <v>0.390826854723006</v>
+        <v>0.31331265932097</v>
       </c>
       <c r="G218"/>
       <c r="H218" t="n">
-        <v>4.0249340499224</v>
+        <v>2.46980929790606</v>
       </c>
       <c r="I218" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="219">
@@ -6686,23 +6678,23 @@
         <v>84</v>
       </c>
       <c r="B219" t="s">
-        <v>71</v>
+        <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>-0.673259396707017</v>
+        <v>-1.38550615703734</v>
       </c>
       <c r="E219" t="n">
-        <v>-1.1698008416434</v>
+        <v>-2.36695006782304</v>
       </c>
       <c r="F219" t="n">
-        <v>0.242081124896929</v>
+        <v>0.0179353523795742</v>
       </c>
       <c r="G219"/>
       <c r="H219" t="n">
-        <v>3.09500211046249</v>
+        <v>2.36695006782304</v>
       </c>
       <c r="I219" t="s">
         <v>11</v>
@@ -6713,25 +6705,25 @@
         <v>84</v>
       </c>
       <c r="B220" t="s">
-        <v>85</v>
+        <v>10</v>
       </c>
       <c r="C220" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.244200454612073</v>
+        <v>-0.467382365575886</v>
       </c>
       <c r="E220" t="n">
-        <v>-1.16606476126988</v>
+        <v>-2.19783241232844</v>
       </c>
       <c r="F220" t="n">
-        <v>0.243588262731164</v>
+        <v>0.0279610507551714</v>
       </c>
       <c r="G220" t="n">
-        <v>0.721615526598251</v>
+        <v>0.334436097267736</v>
       </c>
       <c r="H220" t="n">
-        <v>2.60740007236651</v>
+        <v>2.19783241232844</v>
       </c>
       <c r="I220" t="s">
         <v>11</v>
@@ -6742,303 +6734,25 @@
         <v>84</v>
       </c>
       <c r="B221" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="C221" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.235951201675001</v>
+        <v>-0.673259396707017</v>
       </c>
       <c r="E221" t="n">
-        <v>-1.80370004209605</v>
+        <v>-1.1698008416434</v>
       </c>
       <c r="F221" t="n">
-        <v>0.0712783429559855</v>
-      </c>
-      <c r="G221" t="n">
-        <v>0.503626901967002</v>
-      </c>
+        <v>0.242081124896929</v>
+      </c>
+      <c r="G221"/>
       <c r="H221" t="n">
-        <v>2.55081706198515</v>
+        <v>2.02615449246321</v>
       </c>
       <c r="I221" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="s">
-        <v>86</v>
-      </c>
-      <c r="B222" t="s">
-        <v>15</v>
-      </c>
-      <c r="C222" t="n">
-        <v>6</v>
-      </c>
-      <c r="D222" t="n">
-        <v>0.389552017255811</v>
-      </c>
-      <c r="E222" t="n">
-        <v>1.84413569483074</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G222"/>
-      <c r="H222" t="n">
-        <v>4.51719146878823</v>
-      </c>
-      <c r="I222" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="s">
-        <v>86</v>
-      </c>
-      <c r="B223" t="s">
-        <v>24</v>
-      </c>
-      <c r="C223" t="n">
-        <v>4</v>
-      </c>
-      <c r="D223" t="n">
-        <v>0.519825670239084</v>
-      </c>
-      <c r="E223" t="n">
-        <v>2.1468751925701</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.0318032190620896</v>
-      </c>
-      <c r="G223"/>
-      <c r="H223" t="n">
-        <v>4.29375038514021</v>
-      </c>
-      <c r="I223" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="s">
-        <v>86</v>
-      </c>
-      <c r="B224" t="s">
-        <v>25</v>
-      </c>
-      <c r="C224" t="n">
-        <v>4</v>
-      </c>
-      <c r="D224" t="n">
-        <v>-0.531888018405323</v>
-      </c>
-      <c r="E224" t="n">
-        <v>-2.09437444905346</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G224" t="n">
-        <v>0.381004286040762</v>
-      </c>
-      <c r="H224" t="n">
-        <v>4.18874889810692</v>
-      </c>
-      <c r="I224" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="s">
-        <v>86</v>
-      </c>
-      <c r="B225" t="s">
-        <v>37</v>
-      </c>
-      <c r="C225" t="n">
-        <v>3</v>
-      </c>
-      <c r="D225" t="n">
-        <v>-0.472120445097816</v>
-      </c>
-      <c r="E225" t="n">
-        <v>-2.20017465442735</v>
-      </c>
-      <c r="F225" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G225"/>
-      <c r="H225" t="n">
-        <v>3.81081428699347</v>
-      </c>
-      <c r="I225" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="s">
-        <v>86</v>
-      </c>
-      <c r="B226" t="s">
-        <v>54</v>
-      </c>
-      <c r="C226" t="n">
-        <v>3</v>
-      </c>
-      <c r="D226" t="n">
-        <v>-0.582671827903238</v>
-      </c>
-      <c r="E226" t="n">
-        <v>-1.73074764769325</v>
-      </c>
-      <c r="F226" t="n">
-        <v>0.0834967829299813</v>
-      </c>
-      <c r="G226"/>
-      <c r="H226" t="n">
-        <v>2.99774286088503</v>
-      </c>
-      <c r="I226" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="s">
-        <v>86</v>
-      </c>
-      <c r="B227" t="s">
-        <v>12</v>
-      </c>
-      <c r="C227" t="n">
-        <v>1</v>
-      </c>
-      <c r="D227" t="n">
-        <v>0.282847656074349</v>
-      </c>
-      <c r="E227" t="n">
-        <v>2.48507673142061</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G227" t="n">
-        <v>0.204334507786298</v>
-      </c>
-      <c r="H227" t="n">
-        <v>2.48507673142061</v>
-      </c>
-      <c r="I227" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="s">
-        <v>86</v>
-      </c>
-      <c r="B228" t="s">
-        <v>45</v>
-      </c>
-      <c r="C228" t="n">
-        <v>6</v>
-      </c>
-      <c r="D228" t="n">
-        <v>0.202760189088342</v>
-      </c>
-      <c r="E228" t="n">
-        <v>1.0082954236419</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G228"/>
-      <c r="H228" t="n">
-        <v>2.46980929790606</v>
-      </c>
-      <c r="I228" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="s">
-        <v>86</v>
-      </c>
-      <c r="B229" t="s">
-        <v>16</v>
-      </c>
-      <c r="C229" t="n">
-        <v>1</v>
-      </c>
-      <c r="D229" t="n">
-        <v>-1.38550615703734</v>
-      </c>
-      <c r="E229" t="n">
-        <v>-2.36695006782304</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G229"/>
-      <c r="H229" t="n">
-        <v>2.36695006782304</v>
-      </c>
-      <c r="I229" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="s">
-        <v>86</v>
-      </c>
-      <c r="B230" t="s">
-        <v>10</v>
-      </c>
-      <c r="C230" t="n">
-        <v>1</v>
-      </c>
-      <c r="D230" t="n">
-        <v>-0.467382365575886</v>
-      </c>
-      <c r="E230" t="n">
-        <v>-2.19783241232844</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G230" t="n">
-        <v>0.334436097267736</v>
-      </c>
-      <c r="H230" t="n">
-        <v>2.19783241232844</v>
-      </c>
-      <c r="I230" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="s">
-        <v>86</v>
-      </c>
-      <c r="B231" t="s">
-        <v>71</v>
-      </c>
-      <c r="C231" t="n">
-        <v>3</v>
-      </c>
-      <c r="D231" t="n">
-        <v>-0.673259396707017</v>
-      </c>
-      <c r="E231" t="n">
-        <v>-1.1698008416434</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G231"/>
-      <c r="H231" t="n">
-        <v>2.02615449246321</v>
-      </c>
-      <c r="I231" t="s">
         <v>11</v>
       </c>
     </row>

--- a/Top_TFs_pathways_F23_merged.xlsx
+++ b/Top_TFs_pathways_F23_merged.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
   <si>
     <t xml:space="preserve">pathway</t>
   </si>
@@ -41,43 +41,88 @@
     <t xml:space="preserve">direction</t>
   </si>
   <si>
+    <t xml:space="preserve">HALLMARK_ANDROGEN_RESPONSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXO3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decreases_with_fibrosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCF7L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CUX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HMBOX1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KLF4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BCL11A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFKB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ANGIOGENESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EGR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TP53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Increases_with_fibrosis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPAS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TCF7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAT3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX13</t>
+  </si>
+  <si>
     <t xml:space="preserve">HALLMARK_APICAL_JUNCTION</t>
   </si>
   <si>
-    <t xml:space="preserve">NFKB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decreases_with_fibrosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TCF7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Increases_with_fibrosis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POU2F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TP53</t>
-  </si>
-  <si>
     <t xml:space="preserve">MEF2C</t>
   </si>
   <si>
-    <t xml:space="preserve">CUX1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLF4</t>
+    <t xml:space="preserve">AHR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SOX6</t>
   </si>
   <si>
     <t xml:space="preserve">REL</t>
   </si>
   <si>
-    <t xml:space="preserve">RELA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLF6</t>
+    <t xml:space="preserve">ZNF263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THAP11</t>
   </si>
   <si>
     <t xml:space="preserve">HALLMARK_APICAL_SURFACE</t>
@@ -86,187 +131,172 @@
     <t xml:space="preserve">FOSL2</t>
   </si>
   <si>
+    <t xml:space="preserve">POU2F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CTCF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_APOPTOSIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_COAGULATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEBPB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HHEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESRRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_COMPLEMENT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRF4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_DNA_REPAIR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFX2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFIC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEAD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RELB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_ESTROGEN_RESPONSE_EARLY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_FATTY_ACID_METABOLISM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BACH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARNT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CREB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2F7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IRF3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPARA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFKB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_IL6_JAK_STAT3_SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_INFLAMMATORY_RESPONSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_INTERFERON_GAMMA_RESPONSE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_KRAS_SIGNALING_DN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NFATC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR4A1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_KRAS_SIGNALING_UP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BATF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MITOTIC_SPINDLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MYC_TARGETS_V1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XBP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FOXK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_MYOGENESIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEIS2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZEB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MYC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_TGF_BETA_SIGNALING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ZEB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_TNFA_SIGNALING_VIA_NFKB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HALLMARK_UV_RESPONSE_DN</t>
+  </si>
+  <si>
     <t xml:space="preserve">GABPA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EGR1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POU2F2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2F1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRDM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JUND</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_APOPTOSIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXO3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">THAP11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_COAGULATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HHEX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZEB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SP3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_COMPLEMENT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_DNA_REPAIR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RFX2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRF3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFIC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CREB1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZNF263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_EPITHELIAL_MESENCHYMAL_TRANSITION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_ESTROGEN_RESPONSE_EARLY</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFATC2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NCOA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KLF13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_FATTY_ACID_METABOLISM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MYC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2F7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HIF1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ETS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_G2M_CHECKPOINT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E2F3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_HYPOXIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BACH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_IL2_STAT5_SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IRF4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STAT4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_IL6_JAK_STAT3_SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BATF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_INFLAMMATORY_RESPONSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_INTERFERON_GAMMA_RESPONSE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MITOTIC_SPINDLE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MYC_TARGETS_V1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NR2C2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_MYOGENESIS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_OXIDATIVE_PHOSPHORYLATION</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NR4A1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_TGF_BETA_SIGNALING</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FOXK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MNT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_TNFA_SIGNALING_VIA_NFKB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NFKB2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HALLMARK_UV_RESPONSE_DN</t>
   </si>
 </sst>
 </file>
@@ -632,22 +662,22 @@
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E2" t="n">
-        <v>-2.19783241232844</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G2" t="n">
-        <v>0.334436097267736</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H2" t="n">
-        <v>5.38356795035492</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I2" t="s">
         <v>11</v>
@@ -661,25 +691,23 @@
         <v>12</v>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E3" t="n">
-        <v>2.48507673142061</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G3"/>
       <c r="H3" t="n">
-        <v>3.51442921711283</v>
+        <v>3.0485591372467</v>
       </c>
       <c r="I3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -687,23 +715,23 @@
         <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.406370838177031</v>
+        <v>-0.30928968127718</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.91634437895992</v>
+        <v>-2.85933181562669</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0553212755552297</v>
+        <v>0.00424534465393663</v>
       </c>
       <c r="G4"/>
       <c r="H4" t="n">
-        <v>2.71012021090257</v>
+        <v>2.85933181562669</v>
       </c>
       <c r="I4" t="s">
         <v>11</v>
@@ -714,26 +742,26 @@
         <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.441365633122066</v>
       </c>
       <c r="E5" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.73524643578151</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.00623335899975071</v>
       </c>
       <c r="G5"/>
       <c r="H5" t="n">
-        <v>2.60800171048597</v>
+        <v>2.73524643578151</v>
       </c>
       <c r="I5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -741,23 +769,23 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.38550615703734</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E6" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.00924979246653893</v>
       </c>
       <c r="G6"/>
       <c r="H6" t="n">
-        <v>2.36695006782304</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I6" t="s">
         <v>11</v>
@@ -768,23 +796,25 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.293068543126831</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.22467703206467</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G7"/>
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.454783967358593</v>
+      </c>
       <c r="H7" t="n">
-        <v>2.22467703206467</v>
+        <v>2.41777323005244</v>
       </c>
       <c r="I7" t="s">
         <v>11</v>
@@ -795,23 +825,23 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.30497438363151</v>
+        <v>-1.2978416962463</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.07523837651259</v>
+        <v>-2.35311962153805</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0379644475275991</v>
+        <v>0.0186166440606864</v>
       </c>
       <c r="G8"/>
       <c r="H8" t="n">
-        <v>2.07523837651259</v>
+        <v>2.35311962153805</v>
       </c>
       <c r="I8" t="s">
         <v>11</v>
@@ -822,25 +852,23 @@
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.93662402966198</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.189917068187031</v>
+      </c>
+      <c r="G9"/>
       <c r="H9" t="n">
-        <v>1.93662402966198</v>
+        <v>2.27041460819781</v>
       </c>
       <c r="I9" t="s">
         <v>11</v>
@@ -851,23 +879,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F10" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G10"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H10" t="n">
-        <v>1.91881202039088</v>
+        <v>2.18013147829535</v>
       </c>
       <c r="I10" t="s">
         <v>11</v>
@@ -878,25 +908,25 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.170539952646192</v>
+        <v>-0.202266673175123</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.03910409537338</v>
+        <v>-1.4500017297942</v>
       </c>
       <c r="F11" t="n">
-        <v>0.298756326499217</v>
+        <v>0.147058036847532</v>
       </c>
       <c r="G11" t="n">
-        <v>0.762516147131893</v>
+        <v>0.522636741025254</v>
       </c>
       <c r="H11" t="n">
-        <v>1.79978108753958</v>
+        <v>2.0506121117394</v>
       </c>
       <c r="I11" t="s">
         <v>11</v>
@@ -904,28 +934,28 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G12" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H12" t="n">
-        <v>3.10820440533805</v>
+        <v>4.3602629565907</v>
       </c>
       <c r="I12" t="s">
         <v>11</v>
@@ -933,28 +963,28 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.296782538842574</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.56768616274128</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F13" t="n">
-        <v>0.116954392531525</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G13" t="n">
-        <v>0.581593854164919</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H13" t="n">
-        <v>2.21704303289335</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I13" t="s">
         <v>11</v>
@@ -962,55 +992,55 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.519825670239084</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1468751925701</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0318032190620896</v>
+        <v>0.00924979246653893</v>
       </c>
       <c r="G14"/>
       <c r="H14" t="n">
-        <v>2.1468751925701</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I14" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>25</v>
-      </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E15" t="n">
-        <v>-2.09437444905346</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G15" t="n">
-        <v>0.381004286040762</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H15" t="n">
-        <v>2.09437444905346</v>
+        <v>2.49402250267319</v>
       </c>
       <c r="I15" t="s">
         <v>11</v>
@@ -1018,80 +1048,82 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B16" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.241963225925518</v>
       </c>
       <c r="E16" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.99948416214843</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G16"/>
+        <v>0.0455559938048815</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H16" t="n">
-        <v>1.84413569483074</v>
+        <v>1.99948416214843</v>
       </c>
       <c r="I16" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.353494215052542</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.79303789471052</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F17" t="n">
-        <v>0.072966864969723</v>
+        <v>0.200179065237641</v>
       </c>
       <c r="G17"/>
       <c r="H17" t="n">
-        <v>1.79303789471052</v>
+        <v>1.8116663622585</v>
       </c>
       <c r="I17" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.423447956796695</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.73965095281625</v>
       </c>
       <c r="F18" t="n">
-        <v>0.39915679353664</v>
+        <v>0.0819203265145007</v>
       </c>
       <c r="G18"/>
       <c r="H18" t="n">
-        <v>1.4603407409707</v>
+        <v>1.73965095281625</v>
       </c>
       <c r="I18" t="s">
         <v>11</v>
@@ -1099,57 +1131,57 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.17098099874246</v>
+        <v>0.152085873792625</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.794990361861365</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="F19" t="n">
-        <v>0.426619108659121</v>
+        <v>0.0820557066557046</v>
       </c>
       <c r="G19" t="n">
-        <v>0.846031246698756</v>
+        <v>0.453671257672951</v>
       </c>
       <c r="H19" t="n">
-        <v>1.37696369827145</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="I19" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.219523677256801</v>
+        <v>-0.11089531222503</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.08779706415897</v>
+        <v>-0.96522896220189</v>
       </c>
       <c r="F20" t="n">
-        <v>0.276684705884941</v>
+        <v>0.334430143599031</v>
       </c>
       <c r="G20" t="n">
-        <v>0.749616566006006</v>
+        <v>0.71540633196971</v>
       </c>
       <c r="H20" t="n">
-        <v>1.08779706415897</v>
+        <v>1.67182560347065</v>
       </c>
       <c r="I20" t="s">
         <v>11</v>
@@ -1157,28 +1189,26 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C21" t="n">
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.214989848836869</v>
+        <v>-1.10456835562982</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.05077682479031</v>
+        <v>-1.65249622213236</v>
       </c>
       <c r="F21" t="n">
-        <v>0.293361102116757</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.758446085972238</v>
-      </c>
+        <v>0.0984334346398325</v>
+      </c>
+      <c r="G21"/>
       <c r="H21" t="n">
-        <v>1.05077682479031</v>
+        <v>1.65249622213236</v>
       </c>
       <c r="I21" t="s">
         <v>11</v>
@@ -1186,28 +1216,28 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C22" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F22" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G22" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H22" t="n">
-        <v>6.21640881067611</v>
+        <v>4.87492218535551</v>
       </c>
       <c r="I22" t="s">
         <v>11</v>
@@ -1215,55 +1245,53 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>30</v>
+      </c>
+      <c r="B23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" t="s">
-        <v>15</v>
-      </c>
       <c r="C23" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.389552017255811</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E23" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.00541349094466119</v>
       </c>
       <c r="G23"/>
       <c r="H23" t="n">
-        <v>5.21600342097193</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I23" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.00924979246653893</v>
+      </c>
+      <c r="G24"/>
       <c r="H24" t="n">
-        <v>5.13014873050362</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I24" t="s">
         <v>11</v>
@@ -1271,28 +1299,28 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C25" t="n">
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.89999694915305</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F25" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H25" t="n">
-        <v>4.10121501633284</v>
+        <v>2.41777323005244</v>
       </c>
       <c r="I25" t="s">
         <v>11</v>
@@ -1300,26 +1328,26 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D26" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.36695006782304</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F26" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G26"/>
       <c r="H26" t="n">
-        <v>3.34737288737526</v>
+        <v>2.27041460819781</v>
       </c>
       <c r="I26" t="s">
         <v>11</v>
@@ -1327,28 +1355,26 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.191363321027034</v>
+        <v>-0.269232202247376</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.46328235724133</v>
+        <v>-1.59528635501879</v>
       </c>
       <c r="F27" t="n">
-        <v>0.143390133292888</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0.625163055985475</v>
-      </c>
+        <v>0.110648215490228</v>
+      </c>
+      <c r="G27"/>
       <c r="H27" t="n">
-        <v>3.27199882106775</v>
+        <v>2.25607559913631</v>
       </c>
       <c r="I27" t="s">
         <v>11</v>
@@ -1356,140 +1382,138 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B28" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.384791636175517</v>
+        <v>-1.07923124589441</v>
       </c>
       <c r="E28" t="n">
-        <v>2.30101784326713</v>
+        <v>-2.02709408798513</v>
       </c>
       <c r="F28" t="n">
-        <v>0.0213906225293496</v>
+        <v>0.0426527913776698</v>
       </c>
       <c r="G28"/>
       <c r="H28" t="n">
-        <v>3.25413064121087</v>
+        <v>2.02709408798513</v>
       </c>
       <c r="I28" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B29" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C29" t="n">
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E29" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F29" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.0449216428924176</v>
       </c>
       <c r="G29" t="n">
-        <v>0.204334507786298</v>
+        <v>0.363117998309853</v>
       </c>
       <c r="H29" t="n">
-        <v>2.48507673142061</v>
+        <v>2.00538744474146</v>
       </c>
       <c r="I29" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.293068543126831</v>
+        <v>0.203395249087213</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.22467703206467</v>
+        <v>1.13556042842325</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0261029272182321</v>
+        <v>0.256140578123211</v>
       </c>
       <c r="G30"/>
       <c r="H30" t="n">
-        <v>2.22467703206467</v>
+        <v>1.96684835709375</v>
       </c>
       <c r="I30" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C31" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.296782538842574</v>
+        <v>0.302887223838685</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.56768616274128</v>
+        <v>1.94633140021913</v>
       </c>
       <c r="F31" t="n">
-        <v>0.116954392531525</v>
-      </c>
-      <c r="G31" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.0516149440670543</v>
+      </c>
+      <c r="G31"/>
       <c r="H31" t="n">
-        <v>2.21704303289335</v>
+        <v>1.94633140021913</v>
       </c>
       <c r="I31" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.19783241232844</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F32" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G32" t="n">
-        <v>0.334436097267736</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H32" t="n">
-        <v>7.28938546377511</v>
+        <v>2.41777323005244</v>
       </c>
       <c r="I32" t="s">
         <v>11</v>
@@ -1497,28 +1521,28 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B33" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C33" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F33" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G33" t="n">
-        <v>0.381004286040762</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H33" t="n">
-        <v>4.68316363842221</v>
+        <v>2.18013147829535</v>
       </c>
       <c r="I33" t="s">
         <v>11</v>
@@ -1526,28 +1550,26 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.359164820470093</v>
+        <v>-1.07923124589441</v>
       </c>
       <c r="E34" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.02709408798513</v>
       </c>
       <c r="F34" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.0426527913776698</v>
+      </c>
+      <c r="G34"/>
       <c r="H34" t="n">
-        <v>4.10121501633284</v>
+        <v>2.02709408798513</v>
       </c>
       <c r="I34" t="s">
         <v>11</v>
@@ -1555,26 +1577,28 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B35" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C35" t="n">
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.48587220752926</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E35" t="n">
-        <v>-2.97618080518438</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F35" t="n">
-        <v>0.00291862733391663</v>
-      </c>
-      <c r="G35"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H35" t="n">
-        <v>2.97618080518438</v>
+        <v>1.76354022407205</v>
       </c>
       <c r="I35" t="s">
         <v>11</v>
@@ -1582,26 +1606,26 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.406370838177031</v>
+        <v>-0.269232202247376</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.91634437895992</v>
+        <v>-1.59528635501879</v>
       </c>
       <c r="F36" t="n">
-        <v>0.0553212755552297</v>
+        <v>0.110648215490228</v>
       </c>
       <c r="G36"/>
       <c r="H36" t="n">
-        <v>2.71012021090257</v>
+        <v>1.59528635501879</v>
       </c>
       <c r="I36" t="s">
         <v>11</v>
@@ -1609,53 +1633,55 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B37" t="s">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.302336058691476</v>
       </c>
       <c r="E37" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.51247756372738</v>
       </c>
       <c r="F37" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G37"/>
+        <v>0.130412416117643</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.499421750457285</v>
+      </c>
       <c r="H37" t="n">
-        <v>2.60800171048597</v>
+        <v>1.51247756372738</v>
       </c>
       <c r="I37" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="C38" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.199535805521808</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.10548947172521</v>
       </c>
       <c r="F38" t="n">
-        <v>0.390826854723006</v>
+        <v>0.268947553910649</v>
       </c>
       <c r="G38"/>
       <c r="H38" t="n">
-        <v>2.2703690002806</v>
+        <v>1.10548947172521</v>
       </c>
       <c r="I38" t="s">
         <v>11</v>
@@ -1663,53 +1689,55 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C39" t="n">
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.472120445097816</v>
+        <v>0.143983947836498</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.20017465442735</v>
+        <v>1.10141146801381</v>
       </c>
       <c r="F39" t="n">
-        <v>0.0277945058180277</v>
+        <v>0.270717616506173</v>
       </c>
       <c r="G39"/>
       <c r="H39" t="n">
-        <v>2.20017465442735</v>
+        <v>1.10141146801381</v>
       </c>
       <c r="I39" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B40" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="C40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.30497438363151</v>
+        <v>-0.155331536148406</v>
       </c>
       <c r="E40" t="n">
-        <v>-2.07523837651259</v>
+        <v>-0.684321934561044</v>
       </c>
       <c r="F40" t="n">
-        <v>0.0379644475275991</v>
-      </c>
-      <c r="G40"/>
+        <v>0.493771899112053</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.808256701139861</v>
+      </c>
       <c r="H40" t="n">
-        <v>2.07523837651259</v>
+        <v>0.967777360885623</v>
       </c>
       <c r="I40" t="s">
         <v>11</v>
@@ -1717,26 +1745,28 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C41" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>-0.123629841172641</v>
+        <v>-0.178101024674118</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.994236317803843</v>
+        <v>-0.872122234320205</v>
       </c>
       <c r="F41" t="n">
-        <v>0.320107830807484</v>
-      </c>
-      <c r="G41"/>
+        <v>0.383141697674083</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.751547176206854</v>
+      </c>
       <c r="H41" t="n">
-        <v>1.98847263560769</v>
+        <v>0.872122234320205</v>
       </c>
       <c r="I41" t="s">
         <v>11</v>
@@ -1744,28 +1774,28 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B42" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E42" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F42" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G42" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H42" t="n">
-        <v>5.38356795035492</v>
+        <v>7.23067810714853</v>
       </c>
       <c r="I42" t="s">
         <v>11</v>
@@ -1773,28 +1803,28 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B43" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C43" t="n">
         <v>5</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.09437444905346</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F43" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G43" t="n">
-        <v>0.381004286040762</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H43" t="n">
-        <v>4.68316363842221</v>
+        <v>6.870454934821</v>
       </c>
       <c r="I43" t="s">
         <v>11</v>
@@ -1802,28 +1832,26 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="C44" t="n">
         <v>2</v>
       </c>
       <c r="D44" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E44" t="n">
-        <v>-2.89999694915305</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F44" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G44" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G44"/>
       <c r="H44" t="n">
-        <v>4.10121501633284</v>
+        <v>4.3113136775907</v>
       </c>
       <c r="I44" t="s">
         <v>11</v>
@@ -1831,26 +1859,28 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D45" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E45" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G45"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H45" t="n">
-        <v>3.1115168358807</v>
+        <v>3.94339582208032</v>
       </c>
       <c r="I45" t="s">
         <v>11</v>
@@ -1858,28 +1888,26 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B46" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C46" t="n">
         <v>2</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.346644086928774</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E46" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F46" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G46" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G46"/>
       <c r="H46" t="n">
-        <v>2.73879996796561</v>
+        <v>3.93340958639248</v>
       </c>
       <c r="I46" t="s">
         <v>11</v>
@@ -1887,55 +1915,55 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C47" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D47" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.202266673175123</v>
       </c>
       <c r="E47" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.4500017297942</v>
       </c>
       <c r="F47" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G47"/>
+        <v>0.147058036847532</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.522636741025254</v>
+      </c>
       <c r="H47" t="n">
-        <v>2.60800171048597</v>
+        <v>3.83634397764892</v>
       </c>
       <c r="I47" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B48" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C48" t="n">
         <v>2</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.296782538842574</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E48" t="n">
-        <v>-1.56768616274128</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F48" t="n">
-        <v>0.116954392531525</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.00924979246653893</v>
+      </c>
+      <c r="G48"/>
       <c r="H48" t="n">
-        <v>2.21704303289335</v>
+        <v>3.68074703288006</v>
       </c>
       <c r="I48" t="s">
         <v>11</v>
@@ -1943,53 +1971,55 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B49" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D49" t="n">
-        <v>0.519825670239084</v>
+        <v>0.152085873792625</v>
       </c>
       <c r="E49" t="n">
-        <v>2.1468751925701</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="F49" t="n">
-        <v>0.0318032190620896</v>
-      </c>
-      <c r="G49"/>
+        <v>0.0820557066557046</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.453671257672951</v>
+      </c>
       <c r="H49" t="n">
-        <v>2.1468751925701</v>
+        <v>3.47776188947758</v>
       </c>
       <c r="I49" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B50" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="C50" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.123629841172641</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.994236317803843</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F50" t="n">
-        <v>0.320107830807484</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G50"/>
       <c r="H50" t="n">
-        <v>1.98847263560769</v>
+        <v>3.46811560033332</v>
       </c>
       <c r="I50" t="s">
         <v>11</v>
@@ -1997,82 +2027,84 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C51" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.353494215052542</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E51" t="n">
-        <v>-1.79303789471052</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F51" t="n">
-        <v>0.072966864969723</v>
+        <v>0.200179065237641</v>
       </c>
       <c r="G51"/>
       <c r="H51" t="n">
-        <v>1.79303789471052</v>
+        <v>3.13789818579521</v>
       </c>
       <c r="I51" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B52" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D52" t="n">
-        <v>0.384791636175517</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E52" t="n">
-        <v>2.30101784326713</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F52" t="n">
-        <v>0.0213906225293496</v>
-      </c>
-      <c r="G52"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H52" t="n">
-        <v>3.25413064121087</v>
+        <v>6.89418107004325</v>
       </c>
       <c r="I52" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B53" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="C53" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E53" t="n">
-        <v>-2.19783241232844</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F53" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G53" t="n">
-        <v>0.334436097267736</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H53" t="n">
-        <v>3.10820440533805</v>
+        <v>4.31977368985004</v>
       </c>
       <c r="I53" t="s">
         <v>11</v>
@@ -2080,53 +2112,55 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.317112886110726</v>
       </c>
       <c r="E54" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.40252681339238</v>
       </c>
       <c r="F54" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.0162822408405882</v>
       </c>
       <c r="G54"/>
       <c r="H54" t="n">
-        <v>2.60800171048597</v>
+        <v>4.16129850734215</v>
       </c>
       <c r="I54" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B55" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.0424996815487</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E55" t="n">
-        <v>-2.19286854490787</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F55" t="n">
-        <v>0.0283168515981792</v>
-      </c>
-      <c r="G55"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H55" t="n">
-        <v>2.19286854490787</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I55" t="s">
         <v>11</v>
@@ -2134,28 +2168,26 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B56" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E56" t="n">
-        <v>-2.09437444905346</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F56" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.189917068187031</v>
+      </c>
+      <c r="G56"/>
       <c r="H56" t="n">
-        <v>2.09437444905346</v>
+        <v>2.93109265551205</v>
       </c>
       <c r="I56" t="s">
         <v>11</v>
@@ -2163,26 +2195,26 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B57" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.406370838177031</v>
+        <v>-1.10456835562982</v>
       </c>
       <c r="E57" t="n">
-        <v>-1.91634437895992</v>
+        <v>-1.65249622213236</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0553212755552297</v>
+        <v>0.0984334346398325</v>
       </c>
       <c r="G57"/>
       <c r="H57" t="n">
-        <v>1.91634437895992</v>
+        <v>2.86220741604887</v>
       </c>
       <c r="I57" t="s">
         <v>11</v>
@@ -2190,26 +2222,26 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B58" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.257340060824614</v>
+        <v>-0.300480979410438</v>
       </c>
       <c r="E58" t="n">
-        <v>-1.22890751737433</v>
+        <v>-1.92201619077215</v>
       </c>
       <c r="F58" t="n">
-        <v>0.219106482642347</v>
+        <v>0.0546037205189322</v>
       </c>
       <c r="G58"/>
       <c r="H58" t="n">
-        <v>1.22890751737433</v>
+        <v>2.71814136409065</v>
       </c>
       <c r="I58" t="s">
         <v>11</v>
@@ -2217,26 +2249,26 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="C59" t="n">
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.189243113934208</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.06988637864807</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F59" t="n">
-        <v>0.284670455048985</v>
+        <v>0.00924979246653893</v>
       </c>
       <c r="G59"/>
       <c r="H59" t="n">
-        <v>1.06988637864807</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I59" t="s">
         <v>11</v>
@@ -2244,28 +2276,26 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B60" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.127705649007195</v>
+        <v>-0.812601090410885</v>
       </c>
       <c r="E60" t="n">
-        <v>-1.02792198997847</v>
+        <v>-2.13864819028039</v>
       </c>
       <c r="F60" t="n">
-        <v>0.303986524655079</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0.763093745018922</v>
-      </c>
+        <v>0.0324641715300792</v>
+      </c>
+      <c r="G60"/>
       <c r="H60" t="n">
-        <v>1.02792198997847</v>
+        <v>2.13864819028039</v>
       </c>
       <c r="I60" t="s">
         <v>11</v>
@@ -2273,55 +2303,55 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D61" t="n">
-        <v>0.202760189088342</v>
+        <v>0.30481795415582</v>
       </c>
       <c r="E61" t="n">
-        <v>1.0082954236419</v>
+        <v>1.50767061468641</v>
       </c>
       <c r="F61" t="n">
-        <v>0.31331265932097</v>
+        <v>0.131638849895437</v>
       </c>
       <c r="G61"/>
       <c r="H61" t="n">
-        <v>1.0082954236419</v>
+        <v>2.1321682308809</v>
       </c>
       <c r="I61" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B62" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C62" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E62" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F62" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G62" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H62" t="n">
-        <v>7.28938546377511</v>
+        <v>6.16634300872358</v>
       </c>
       <c r="I62" t="s">
         <v>11</v>
@@ -2329,28 +2359,28 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C63" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E63" t="n">
-        <v>-2.09437444905346</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F63" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G63" t="n">
-        <v>0.381004286040762</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H63" t="n">
-        <v>6.28312334716039</v>
+        <v>5.32183150868606</v>
       </c>
       <c r="I63" t="s">
         <v>11</v>
@@ -2358,82 +2388,84 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C64" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E64" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G64"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H64" t="n">
-        <v>5.21600342097193</v>
+        <v>4.66588885995378</v>
       </c>
       <c r="I64" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C65" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D65" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.317112886110726</v>
       </c>
       <c r="E65" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.40252681339238</v>
       </c>
       <c r="F65" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G65" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.0162822408405882</v>
+      </c>
+      <c r="G65"/>
       <c r="H65" t="n">
-        <v>3.51442921711283</v>
+        <v>4.16129850734215</v>
       </c>
       <c r="I65" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C66" t="n">
         <v>2</v>
       </c>
       <c r="D66" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E66" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G66"/>
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H66" t="n">
-        <v>3.34737288737526</v>
+        <v>2.8360461221661</v>
       </c>
       <c r="I66" t="s">
         <v>11</v>
@@ -2441,28 +2473,26 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C67" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.17098099874246</v>
+        <v>-0.528075829615833</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.794990361861365</v>
+        <v>-1.66952321290248</v>
       </c>
       <c r="F67" t="n">
-        <v>0.426619108659121</v>
-      </c>
-      <c r="G67" t="n">
-        <v>0.846031246698756</v>
-      </c>
+        <v>0.0950137339439168</v>
+      </c>
+      <c r="G67"/>
       <c r="H67" t="n">
-        <v>2.86637851319082</v>
+        <v>2.3610623703834</v>
       </c>
       <c r="I67" t="s">
         <v>11</v>
@@ -2470,26 +2500,26 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="C68" t="n">
         <v>2</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.406370838177031</v>
+        <v>-1.10456835562982</v>
       </c>
       <c r="E68" t="n">
-        <v>-1.91634437895992</v>
+        <v>-1.65249622213236</v>
       </c>
       <c r="F68" t="n">
-        <v>0.0553212755552297</v>
+        <v>0.0984334346398325</v>
       </c>
       <c r="G68"/>
       <c r="H68" t="n">
-        <v>2.71012021090257</v>
+        <v>2.33698256910989</v>
       </c>
       <c r="I68" t="s">
         <v>11</v>
@@ -2497,26 +2527,26 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B69" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C69" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F69" t="n">
-        <v>0.390826854723006</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G69"/>
       <c r="H69" t="n">
-        <v>2.57435646818263</v>
+        <v>2.27041460819781</v>
       </c>
       <c r="I69" t="s">
         <v>11</v>
@@ -2524,53 +2554,55 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D70" t="n">
-        <v>0.568852661112965</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E70" t="n">
-        <v>1.69911620492032</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F70" t="n">
-        <v>0.0892972906656036</v>
+        <v>0.200179065237641</v>
       </c>
       <c r="G70"/>
       <c r="H70" t="n">
-        <v>2.40291318104622</v>
+        <v>2.21882908584876</v>
       </c>
       <c r="I70" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B71" t="s">
         <v>38</v>
       </c>
       <c r="C71" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D71" t="n">
-        <v>-0.123629841172641</v>
+        <v>-0.302336058691476</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.994236317803843</v>
+        <v>-1.51247756372738</v>
       </c>
       <c r="F71" t="n">
-        <v>0.320107830807484</v>
-      </c>
-      <c r="G71"/>
+        <v>0.130412416117643</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.499421750457285</v>
+      </c>
       <c r="H71" t="n">
-        <v>2.22317999230848</v>
+        <v>2.13896628340827</v>
       </c>
       <c r="I71" t="s">
         <v>11</v>
@@ -2578,55 +2610,53 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B72" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C72" t="n">
         <v>2</v>
       </c>
       <c r="D72" t="n">
-        <v>-0.472120445097816</v>
+        <v>0.302887223838685</v>
       </c>
       <c r="E72" t="n">
-        <v>-2.20017465442735</v>
+        <v>1.94633140021913</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0277945058180277</v>
+        <v>0.0516149440670543</v>
       </c>
       <c r="G72"/>
       <c r="H72" t="n">
-        <v>3.1115168358807</v>
+        <v>2.75252826306251</v>
       </c>
       <c r="I72" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B73" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.00528774978176</v>
       </c>
       <c r="E73" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.36049646431568</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G73" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.018250492291681</v>
+      </c>
+      <c r="G73"/>
       <c r="H73" t="n">
-        <v>2.96189275053909</v>
+        <v>2.36049646431568</v>
       </c>
       <c r="I73" t="s">
         <v>11</v>
@@ -2634,84 +2664,82 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B74" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D74" t="n">
-        <v>-0.359164820470093</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E74" t="n">
-        <v>-2.89999694915305</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F74" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G74" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G74"/>
       <c r="H74" t="n">
-        <v>2.89999694915305</v>
+        <v>2.21882908584876</v>
       </c>
       <c r="I74" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B75" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E75" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G75"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H75" t="n">
-        <v>2.60800171048597</v>
+        <v>2.18013147829535</v>
       </c>
       <c r="I75" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B76" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C76" t="n">
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>-0.235951201675001</v>
+        <v>-1.07923124589441</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.80370004209605</v>
+        <v>-2.02709408798513</v>
       </c>
       <c r="F76" t="n">
-        <v>0.0712783429559855</v>
-      </c>
-      <c r="G76" t="n">
-        <v>0.503626901967002</v>
-      </c>
+        <v>0.0426527913776698</v>
+      </c>
+      <c r="G76"/>
       <c r="H76" t="n">
-        <v>1.80370004209605</v>
+        <v>2.02709408798513</v>
       </c>
       <c r="I76" t="s">
         <v>11</v>
@@ -2719,53 +2747,55 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B77" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E77" t="n">
-        <v>1.0082954236419</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F77" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G77"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H77" t="n">
-        <v>1.74641890278696</v>
+        <v>1.76354022407205</v>
       </c>
       <c r="I77" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B78" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="C78" t="n">
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>-0.24184789221507</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.71740931132057</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F78" t="n">
-        <v>0.0859044115550883</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G78"/>
       <c r="H78" t="n">
-        <v>1.71740931132057</v>
+        <v>1.31082448521506</v>
       </c>
       <c r="I78" t="s">
         <v>11</v>
@@ -2773,55 +2803,55 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B79" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C79" t="n">
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0.568852661112965</v>
+        <v>-0.161954876364702</v>
       </c>
       <c r="E79" t="n">
-        <v>1.69911620492032</v>
+        <v>-1.02567454265089</v>
       </c>
       <c r="F79" t="n">
-        <v>0.0892972906656036</v>
+        <v>0.305045017836696</v>
       </c>
       <c r="G79"/>
       <c r="H79" t="n">
-        <v>1.69911620492032</v>
+        <v>1.02567454265089</v>
       </c>
       <c r="I79" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B80" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>-0.140329115706343</v>
+        <v>-0.11089531222503</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.959469282447805</v>
+        <v>-0.96522896220189</v>
       </c>
       <c r="F80" t="n">
-        <v>0.337322387113442</v>
+        <v>0.334430143599031</v>
       </c>
       <c r="G80" t="n">
-        <v>0.796124318021208</v>
+        <v>0.71540633196971</v>
       </c>
       <c r="H80" t="n">
-        <v>1.66184954550125</v>
+        <v>0.96522896220189</v>
       </c>
       <c r="I80" t="s">
         <v>11</v>
@@ -2829,28 +2859,26 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B81" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D81" t="n">
-        <v>-0.146567277237516</v>
+        <v>-0.370869206784898</v>
       </c>
       <c r="E81" t="n">
-        <v>-1.37581390411533</v>
+        <v>-0.587526914204648</v>
       </c>
       <c r="F81" t="n">
-        <v>0.168879255629964</v>
-      </c>
-      <c r="G81" t="n">
-        <v>0.662863555608717</v>
-      </c>
+        <v>0.556849880034685</v>
+      </c>
+      <c r="G81"/>
       <c r="H81" t="n">
-        <v>1.37581390411533</v>
+        <v>0.830888530327427</v>
       </c>
       <c r="I81" t="s">
         <v>11</v>
@@ -2858,55 +2886,57 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
+        <v>19</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D82" t="n">
-        <v>0.568852661112965</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E82" t="n">
-        <v>1.69911620492032</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F82" t="n">
-        <v>0.0892972906656036</v>
-      </c>
-      <c r="G82"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H82" t="n">
-        <v>1.69911620492032</v>
+        <v>5.76808571699311</v>
       </c>
       <c r="I82" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B83" t="s">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="C83" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D83" t="n">
-        <v>-0.127705649007195</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E83" t="n">
-        <v>-1.02792198997847</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F83" t="n">
-        <v>0.303986524655079</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G83" t="n">
-        <v>0.763093745018922</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H83" t="n">
-        <v>1.4537012192891</v>
+        <v>4.66588885995378</v>
       </c>
       <c r="I83" t="s">
         <v>11</v>
@@ -2914,26 +2944,26 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B84" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C84" t="n">
         <v>2</v>
       </c>
       <c r="D84" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E84" t="n">
-        <v>-0.843128119908009</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F84" t="n">
-        <v>0.39915679353664</v>
+        <v>0.00229941650586847</v>
       </c>
       <c r="G84"/>
       <c r="H84" t="n">
-        <v>1.19236322199204</v>
+        <v>4.3113136775907</v>
       </c>
       <c r="I84" t="s">
         <v>11</v>
@@ -2941,26 +2971,26 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B85" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C85" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D85" t="n">
-        <v>-0.141237121743142</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.505075071717537</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F85" t="n">
-        <v>0.613506109324499</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G85"/>
       <c r="H85" t="n">
-        <v>1.01015014343507</v>
+        <v>3.21085113112334</v>
       </c>
       <c r="I85" t="s">
         <v>11</v>
@@ -2968,55 +2998,53 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B86" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="C86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0728339894275881</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E86" t="n">
-        <v>0.706727814492832</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F86" t="n">
-        <v>0.47973564103236</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.870332217592113</v>
-      </c>
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G86"/>
       <c r="H86" t="n">
-        <v>0.706727814492832</v>
+        <v>2.86449603252429</v>
       </c>
       <c r="I86" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="C87" t="n">
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>-0.0813258659038187</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.382914639728419</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F87" t="n">
-        <v>0.701783056225352</v>
+        <v>0.00924979246653893</v>
       </c>
       <c r="G87"/>
       <c r="H87" t="n">
-        <v>0.382914639728419</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I87" t="s">
         <v>11</v>
@@ -3024,53 +3052,55 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C88" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D88" t="n">
-        <v>0.0417765291221938</v>
+        <v>-0.791912701347419</v>
       </c>
       <c r="E88" t="n">
-        <v>0.213160526557962</v>
+        <v>-1.29038085805786</v>
       </c>
       <c r="F88" t="n">
-        <v>0.831201755923087</v>
+        <v>0.196918454952233</v>
       </c>
       <c r="G88"/>
       <c r="H88" t="n">
-        <v>0.369204862166525</v>
+        <v>2.58076171611573</v>
       </c>
       <c r="I88" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B89" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D89" t="n">
-        <v>-0.464681491897395</v>
+        <v>-0.357413540274438</v>
       </c>
       <c r="E89" t="n">
-        <v>-0.24304685362388</v>
+        <v>-1.79254788571914</v>
       </c>
       <c r="F89" t="n">
-        <v>0.807969101477861</v>
-      </c>
-      <c r="G89"/>
+        <v>0.0730452457883126</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.441975579433005</v>
+      </c>
       <c r="H89" t="n">
-        <v>0.24304685362388</v>
+        <v>2.53504553118723</v>
       </c>
       <c r="I89" t="s">
         <v>11</v>
@@ -3078,55 +3108,57 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B90" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="C90" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D90" t="n">
-        <v>-0.0182683792598074</v>
+        <v>0.152085873792625</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.127064915281692</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="F90" t="n">
-        <v>0.898889019880745</v>
-      </c>
-      <c r="G90"/>
+        <v>0.0820557066557046</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.453671257672951</v>
+      </c>
       <c r="H90" t="n">
-        <v>0.220082889127326</v>
+        <v>2.45914901540174</v>
       </c>
       <c r="I90" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B91" t="s">
-        <v>60</v>
+        <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D91" t="n">
-        <v>-0.0158910153931639</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E91" t="n">
-        <v>-0.176388165960046</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F91" t="n">
-        <v>0.859989001102471</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G91" t="n">
-        <v>0.968466379060083</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H91" t="n">
-        <v>0.176388165960046</v>
+        <v>2.41777323005244</v>
       </c>
       <c r="I91" t="s">
         <v>11</v>
@@ -3134,55 +3166,55 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B92" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C92" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D92" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E92" t="n">
-        <v>1.84413569483074</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F92" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G92"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H92" t="n">
-        <v>6.38827343899636</v>
+        <v>4.34525723111561</v>
       </c>
       <c r="I92" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B93" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D93" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E93" t="n">
-        <v>-2.19783241232844</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F93" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G93"/>
       <c r="H93" t="n">
-        <v>4.39566482465688</v>
+        <v>4.3113136775907</v>
       </c>
       <c r="I93" t="s">
         <v>11</v>
@@ -3190,26 +3222,28 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B94" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="D94" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E94" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F94" t="n">
-        <v>0.39915679353664</v>
-      </c>
-      <c r="G94"/>
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.454783967358593</v>
+      </c>
       <c r="H94" t="n">
-        <v>3.03994166811388</v>
+        <v>3.82283513637399</v>
       </c>
       <c r="I94" t="s">
         <v>11</v>
@@ -3217,28 +3251,26 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B95" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C95" t="n">
         <v>2</v>
       </c>
       <c r="D95" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E95" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.00924979246653893</v>
+      </c>
+      <c r="G95"/>
       <c r="H95" t="n">
-        <v>2.96189275053909</v>
+        <v>3.68074703288006</v>
       </c>
       <c r="I95" t="s">
         <v>11</v>
@@ -3246,26 +3278,26 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B96" t="s">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="C96" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D96" t="n">
-        <v>-0.272696592226143</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E96" t="n">
-        <v>-1.27637770916738</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F96" t="n">
-        <v>0.201822032086846</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G96"/>
       <c r="H96" t="n">
-        <v>2.55275541833476</v>
+        <v>3.46811560033332</v>
       </c>
       <c r="I96" t="s">
         <v>11</v>
@@ -3273,57 +3305,57 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B97" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D97" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E97" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F97" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G97" t="n">
-        <v>0.204334507786298</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H97" t="n">
-        <v>2.48507673142061</v>
+        <v>3.08317150436179</v>
       </c>
       <c r="I97" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B98" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D98" t="n">
-        <v>-0.140329115706343</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E98" t="n">
-        <v>-0.959469282447805</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F98" t="n">
-        <v>0.337322387113442</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G98" t="n">
-        <v>0.796124318021208</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H98" t="n">
-        <v>2.14543853787624</v>
+        <v>3.0545412692842</v>
       </c>
       <c r="I98" t="s">
         <v>11</v>
@@ -3331,138 +3363,136 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B99" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C99" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D99" t="n">
-        <v>-1.30497438363151</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E99" t="n">
-        <v>-2.07523837651259</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0379644475275991</v>
+        <v>0.200179065237641</v>
       </c>
       <c r="G99"/>
       <c r="H99" t="n">
-        <v>2.07523837651259</v>
+        <v>2.86449603252429</v>
       </c>
       <c r="I99" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B100" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C100" t="n">
         <v>3</v>
       </c>
       <c r="D100" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.269232202247376</v>
       </c>
       <c r="E100" t="n">
-        <v>1.0082954236419</v>
+        <v>-1.59528635501879</v>
       </c>
       <c r="F100" t="n">
-        <v>0.31331265932097</v>
+        <v>0.110648215490228</v>
       </c>
       <c r="G100"/>
       <c r="H100" t="n">
-        <v>1.74641890278696</v>
+        <v>2.76311701951391</v>
       </c>
       <c r="I100" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B101" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C101" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" t="n">
-        <v>-0.121791813728833</v>
+        <v>0.30481795415582</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.858118822727544</v>
+        <v>1.50767061468641</v>
       </c>
       <c r="F101" t="n">
-        <v>0.390826854723006</v>
+        <v>0.131638849895437</v>
       </c>
       <c r="G101"/>
       <c r="H101" t="n">
-        <v>1.71623764545509</v>
+        <v>2.61136210571546</v>
       </c>
       <c r="I101" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B102" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>-0.467382365575886</v>
+        <v>0.137369704274393</v>
       </c>
       <c r="E102" t="n">
-        <v>-2.19783241232844</v>
+        <v>1.43386613239452</v>
       </c>
       <c r="F102" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.151610468290517</v>
       </c>
       <c r="G102" t="n">
-        <v>0.334436097267736</v>
+        <v>0.531584204443626</v>
       </c>
       <c r="H102" t="n">
-        <v>5.81491798641822</v>
+        <v>1.43386613239452</v>
       </c>
       <c r="I102" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B103" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="C103" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D103" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.146410375954783</v>
       </c>
       <c r="E103" t="n">
-        <v>-2.09437444905346</v>
+        <v>-0.743378356718217</v>
       </c>
       <c r="F103" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.457252644014291</v>
+      </c>
+      <c r="G103"/>
       <c r="H103" t="n">
-        <v>4.68316363842221</v>
+        <v>1.05129575404553</v>
       </c>
       <c r="I103" t="s">
         <v>11</v>
@@ -3470,53 +3500,55 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B104" t="s">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="C104" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0.389552017255811</v>
+        <v>0.274779811495567</v>
       </c>
       <c r="E104" t="n">
-        <v>1.84413569483074</v>
+        <v>0.981963405750682</v>
       </c>
       <c r="F104" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.326117876745646</v>
       </c>
       <c r="G104"/>
       <c r="H104" t="n">
-        <v>4.51719146878823</v>
+        <v>0.981963405750682</v>
       </c>
       <c r="I104" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
+        <v>59</v>
+      </c>
+      <c r="B105" t="s">
         <v>63</v>
       </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
       <c r="C105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.103792110905303</v>
       </c>
       <c r="E105" t="n">
-        <v>-2.36695006782304</v>
+        <v>-0.832894223389201</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G105"/>
+        <v>0.404904387838539</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.762330680616371</v>
+      </c>
       <c r="H105" t="n">
-        <v>3.34737288737526</v>
+        <v>0.832894223389201</v>
       </c>
       <c r="I105" t="s">
         <v>11</v>
@@ -3524,26 +3556,26 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B106" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C106" t="n">
         <v>2</v>
       </c>
       <c r="D106" t="n">
-        <v>-1.30497438363151</v>
+        <v>-0.370869206784898</v>
       </c>
       <c r="E106" t="n">
-        <v>-2.07523837651259</v>
+        <v>-0.587526914204648</v>
       </c>
       <c r="F106" t="n">
-        <v>0.0379644475275991</v>
+        <v>0.556849880034685</v>
       </c>
       <c r="G106"/>
       <c r="H106" t="n">
-        <v>2.93483025722123</v>
+        <v>0.830888530327427</v>
       </c>
       <c r="I106" t="s">
         <v>11</v>
@@ -3551,28 +3583,28 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B107" t="s">
         <v>64</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D107" t="n">
-        <v>-0.350420430655839</v>
+        <v>-0.0477851818645616</v>
       </c>
       <c r="E107" t="n">
-        <v>-1.56791478927012</v>
+        <v>-0.405353775737904</v>
       </c>
       <c r="F107" t="n">
-        <v>0.116901019836926</v>
+        <v>0.685217483368185</v>
       </c>
       <c r="G107" t="n">
-        <v>0.581593854164919</v>
+        <v>0.901860784269583</v>
       </c>
       <c r="H107" t="n">
-        <v>2.21736635963116</v>
+        <v>0.702093334617931</v>
       </c>
       <c r="I107" t="s">
         <v>11</v>
@@ -3580,28 +3612,26 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B108" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="C108" t="n">
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.79547416333653</v>
       </c>
       <c r="E108" t="n">
-        <v>-1.93662402966198</v>
+        <v>-0.418706958638416</v>
       </c>
       <c r="F108" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.675430309461999</v>
+      </c>
+      <c r="G108"/>
       <c r="H108" t="n">
-        <v>1.93662402966198</v>
+        <v>0.418706958638416</v>
       </c>
       <c r="I108" t="s">
         <v>11</v>
@@ -3609,28 +3639,26 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B109" t="s">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>-0.296782538842574</v>
+        <v>-0.066218907268106</v>
       </c>
       <c r="E109" t="n">
-        <v>-1.56768616274128</v>
+        <v>-0.388752863027231</v>
       </c>
       <c r="F109" t="n">
-        <v>0.116954392531525</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.697458973126591</v>
+      </c>
+      <c r="G109"/>
       <c r="H109" t="n">
-        <v>1.56768616274128</v>
+        <v>0.388752863027231</v>
       </c>
       <c r="I109" t="s">
         <v>11</v>
@@ -3638,26 +3666,28 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B110" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="C110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.030255859194947</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.858118822727544</v>
+        <v>-0.357673375742895</v>
       </c>
       <c r="F110" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G110"/>
+        <v>0.720587759822087</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.923084868347736</v>
+      </c>
       <c r="H110" t="n">
-        <v>1.4863053998953</v>
+        <v>0.357673375742895</v>
       </c>
       <c r="I110" t="s">
         <v>11</v>
@@ -3665,28 +3695,26 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B111" t="s">
-        <v>21</v>
+        <v>68</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>-0.170539952646192</v>
+        <v>-0.0749436558670191</v>
       </c>
       <c r="E111" t="n">
-        <v>-1.03910409537338</v>
+        <v>-0.329212623811751</v>
       </c>
       <c r="F111" t="n">
-        <v>0.298756326499217</v>
-      </c>
-      <c r="G111" t="n">
-        <v>0.762516147131893</v>
-      </c>
+        <v>0.7419949818703</v>
+      </c>
+      <c r="G111"/>
       <c r="H111" t="n">
-        <v>1.46951510439445</v>
+        <v>0.329212623811751</v>
       </c>
       <c r="I111" t="s">
         <v>11</v>
@@ -3694,84 +3722,82 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B112" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="C112" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D112" t="n">
-        <v>-0.467382365575886</v>
+        <v>0.210949149380054</v>
       </c>
       <c r="E112" t="n">
-        <v>-2.19783241232844</v>
+        <v>1.28104157000055</v>
       </c>
       <c r="F112" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G112"/>
       <c r="H112" t="n">
-        <v>6.9501563383002</v>
+        <v>4.79321865315705</v>
       </c>
       <c r="I112" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B113" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C113" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D113" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E113" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F113" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G113" t="n">
-        <v>0.204334507786298</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H113" t="n">
-        <v>4.3042791595277</v>
+        <v>4.3602629565907</v>
       </c>
       <c r="I113" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B114" t="s">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="C114" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D114" t="n">
-        <v>-0.582671827903238</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E114" t="n">
-        <v>-1.73074764769325</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F114" t="n">
-        <v>0.0834967829299813</v>
+        <v>0.00229941650586847</v>
       </c>
       <c r="G114"/>
       <c r="H114" t="n">
-        <v>2.99774286088503</v>
+        <v>4.3113136775907</v>
       </c>
       <c r="I114" t="s">
         <v>11</v>
@@ -3779,28 +3805,28 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B115" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D115" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E115" t="n">
-        <v>-2.89999694915305</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F115" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G115" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H115" t="n">
-        <v>2.89999694915305</v>
+        <v>4.18770607563074</v>
       </c>
       <c r="I115" t="s">
         <v>11</v>
@@ -3808,28 +3834,26 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B116" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C116" t="n">
         <v>2</v>
       </c>
       <c r="D116" t="n">
-        <v>-0.346644086928774</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E116" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F116" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.00924979246653893</v>
+      </c>
+      <c r="G116"/>
       <c r="H116" t="n">
-        <v>2.73879996796561</v>
+        <v>3.68074703288006</v>
       </c>
       <c r="I116" t="s">
         <v>11</v>
@@ -3837,26 +3861,26 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B117" t="s">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="C117" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D117" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.284583943390734</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.59803096322438</v>
       </c>
       <c r="F117" t="n">
-        <v>0.390826854723006</v>
+        <v>0.110036086327583</v>
       </c>
       <c r="G117"/>
       <c r="H117" t="n">
-        <v>2.57435646818263</v>
+        <v>3.19606192644875</v>
       </c>
       <c r="I117" t="s">
         <v>11</v>
@@ -3864,26 +3888,28 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B118" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C118" t="n">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E118" t="n">
-        <v>-2.36695006782304</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F118" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G118"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H118" t="n">
-        <v>2.36695006782304</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I118" t="s">
         <v>11</v>
@@ -3891,26 +3917,28 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B119" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D119" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E119" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F119" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G119"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H119" t="n">
-        <v>2.20017465442735</v>
+        <v>3.0545412692842</v>
       </c>
       <c r="I119" t="s">
         <v>11</v>
@@ -3918,28 +3946,26 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B120" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.30928968127718</v>
       </c>
       <c r="E120" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.85933181562669</v>
       </c>
       <c r="F120" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G120" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.00424534465393663</v>
+      </c>
+      <c r="G120"/>
       <c r="H120" t="n">
-        <v>2.09437444905346</v>
+        <v>2.85933181562669</v>
       </c>
       <c r="I120" t="s">
         <v>11</v>
@@ -3947,28 +3973,26 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B121" t="s">
-        <v>67</v>
+        <v>14</v>
       </c>
       <c r="C121" t="n">
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>-0.24395134664857</v>
+        <v>-0.441365633122066</v>
       </c>
       <c r="E121" t="n">
-        <v>-2.08608978977804</v>
+        <v>-2.73524643578151</v>
       </c>
       <c r="F121" t="n">
-        <v>0.0369704904012726</v>
-      </c>
-      <c r="G121" t="n">
-        <v>0.386605699624737</v>
-      </c>
+        <v>0.00623335899975071</v>
+      </c>
+      <c r="G121"/>
       <c r="H121" t="n">
-        <v>2.08608978977804</v>
+        <v>2.73524643578151</v>
       </c>
       <c r="I121" t="s">
         <v>11</v>
@@ -3976,28 +4000,28 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B122" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C122" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D122" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E122" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F122" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G122" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H122" t="n">
-        <v>6.59349723698531</v>
+        <v>7.23067810714853</v>
       </c>
       <c r="I122" t="s">
         <v>11</v>
@@ -4005,28 +4029,28 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B123" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D123" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E123" t="n">
-        <v>-2.09437444905346</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F123" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G123" t="n">
-        <v>0.381004286040762</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H123" t="n">
-        <v>3.62756295583467</v>
+        <v>4.34525723111561</v>
       </c>
       <c r="I123" t="s">
         <v>11</v>
@@ -4034,82 +4058,84 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B124" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C124" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D124" t="n">
-        <v>-0.346644086928774</v>
+        <v>0.152085873792625</v>
       </c>
       <c r="E124" t="n">
-        <v>-1.93662402966198</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="F124" t="n">
-        <v>0.0527913184011619</v>
+        <v>0.0820557066557046</v>
       </c>
       <c r="G124" t="n">
-        <v>0.435171678712281</v>
+        <v>0.453671257672951</v>
       </c>
       <c r="H124" t="n">
-        <v>3.35433121453333</v>
+        <v>3.47776188947758</v>
       </c>
       <c r="I124" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B125" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C125" t="n">
         <v>3</v>
       </c>
       <c r="D125" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E125" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F125" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G125"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H125" t="n">
-        <v>3.19413671949818</v>
+        <v>3.0545412692842</v>
       </c>
       <c r="I125" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B126" t="s">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>-1.48587220752926</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E126" t="n">
-        <v>-2.97618080518438</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F126" t="n">
-        <v>0.00291862733391663</v>
+        <v>0.00229941650586847</v>
       </c>
       <c r="G126"/>
       <c r="H126" t="n">
-        <v>2.97618080518438</v>
+        <v>3.0485591372467</v>
       </c>
       <c r="I126" t="s">
         <v>11</v>
@@ -4117,28 +4143,28 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B127" t="s">
-        <v>67</v>
+        <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D127" t="n">
-        <v>-0.24395134664857</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E127" t="n">
-        <v>-2.08608978977804</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F127" t="n">
-        <v>0.0369704904012726</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G127" t="n">
-        <v>0.386605699624737</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H127" t="n">
-        <v>2.95017647303215</v>
+        <v>2.9611553636946</v>
       </c>
       <c r="I127" t="s">
         <v>11</v>
@@ -4146,26 +4172,26 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B128" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C128" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D128" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.528075829615833</v>
       </c>
       <c r="E128" t="n">
-        <v>-1.1698008416434</v>
+        <v>-1.66952321290248</v>
       </c>
       <c r="F128" t="n">
-        <v>0.242081124896929</v>
+        <v>0.0950137339439168</v>
       </c>
       <c r="G128"/>
       <c r="H128" t="n">
-        <v>2.86541516270464</v>
+        <v>2.89169902916273</v>
       </c>
       <c r="I128" t="s">
         <v>11</v>
@@ -4173,26 +4199,28 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D129" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E129" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F129" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G129"/>
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H129" t="n">
-        <v>2.36695006782304</v>
+        <v>2.8360461221661</v>
       </c>
       <c r="I129" t="s">
         <v>11</v>
@@ -4200,26 +4228,28 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B130" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C130" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D130" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.241963225925518</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.99948416214843</v>
       </c>
       <c r="F130" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G130"/>
+        <v>0.0455559938048815</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H130" t="n">
-        <v>2.1019532543603</v>
+        <v>2.82769761986051</v>
       </c>
       <c r="I130" t="s">
         <v>11</v>
@@ -4227,55 +4257,57 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C131" t="n">
         <v>4</v>
       </c>
       <c r="D131" t="n">
-        <v>0.160200568560385</v>
+        <v>-0.265641519314599</v>
       </c>
       <c r="E131" t="n">
-        <v>0.973907884018594</v>
+        <v>-1.39356722832242</v>
       </c>
       <c r="F131" t="n">
-        <v>0.330102278801738</v>
-      </c>
-      <c r="G131"/>
+        <v>0.163448330518012</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.549337767565592</v>
+      </c>
       <c r="H131" t="n">
-        <v>1.94781576803719</v>
+        <v>2.78713445664484</v>
       </c>
       <c r="I131" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B132" t="s">
+        <v>19</v>
+      </c>
+      <c r="C132" t="n">
         <v>10</v>
       </c>
-      <c r="C132" t="n">
-        <v>14</v>
-      </c>
       <c r="D132" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E132" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F132" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G132" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H132" t="n">
-        <v>8.22353588047989</v>
+        <v>6.89418107004325</v>
       </c>
       <c r="I132" t="s">
         <v>11</v>
@@ -4283,28 +4315,26 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B133" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C133" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D133" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E133" t="n">
-        <v>-2.09437444905346</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F133" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G133" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G133"/>
       <c r="H133" t="n">
-        <v>4.68316363842221</v>
+        <v>4.3113136775907</v>
       </c>
       <c r="I133" t="s">
         <v>11</v>
@@ -4312,53 +4342,57 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B134" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C134" t="n">
         <v>5</v>
       </c>
       <c r="D134" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E134" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F134" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G134"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H134" t="n">
-        <v>4.12361277337535</v>
+        <v>3.94339582208032</v>
       </c>
       <c r="I134" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B135" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C135" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D135" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E135" t="n">
-        <v>-1.1698008416434</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F135" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G135"/>
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H135" t="n">
-        <v>3.50940252493021</v>
+        <v>3.47343294315293</v>
       </c>
       <c r="I135" t="s">
         <v>11</v>
@@ -4366,28 +4400,26 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B136" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D136" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.317112886110726</v>
       </c>
       <c r="E136" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.40252681339238</v>
       </c>
       <c r="F136" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G136" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0162822408405882</v>
+      </c>
+      <c r="G136"/>
       <c r="H136" t="n">
-        <v>3.35433121453333</v>
+        <v>3.39768600346451</v>
       </c>
       <c r="I136" t="s">
         <v>11</v>
@@ -4395,26 +4427,28 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B137" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C137" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D137" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.241963225925518</v>
       </c>
       <c r="E137" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.99948416214843</v>
       </c>
       <c r="F137" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G137"/>
+        <v>0.0455559938048815</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H137" t="n">
-        <v>2.97261079979059</v>
+        <v>2.82769761986051</v>
       </c>
       <c r="I137" t="s">
         <v>11</v>
@@ -4422,28 +4456,26 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B138" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C138" t="n">
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>-0.359164820470093</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E138" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F138" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G138" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G138"/>
       <c r="H138" t="n">
-        <v>2.89999694915305</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I138" t="s">
         <v>11</v>
@@ -4451,28 +4483,26 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B139" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D139" t="n">
-        <v>-0.191363321027034</v>
+        <v>-0.300480979410438</v>
       </c>
       <c r="E139" t="n">
-        <v>-1.46328235724133</v>
+        <v>-1.92201619077215</v>
       </c>
       <c r="F139" t="n">
-        <v>0.143390133292888</v>
-      </c>
-      <c r="G139" t="n">
-        <v>0.625163055985475</v>
-      </c>
+        <v>0.0546037205189322</v>
+      </c>
+      <c r="G139"/>
       <c r="H139" t="n">
-        <v>2.53447938856114</v>
+        <v>2.71814136409065</v>
       </c>
       <c r="I139" t="s">
         <v>11</v>
@@ -4480,26 +4510,28 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B140" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="C140" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D140" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.11089531222503</v>
       </c>
       <c r="E140" t="n">
-        <v>-2.36695006782304</v>
+        <v>-0.96522896220189</v>
       </c>
       <c r="F140" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G140"/>
+        <v>0.334430143599031</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.71540633196971</v>
+      </c>
       <c r="H140" t="n">
-        <v>2.36695006782304</v>
+        <v>2.36431844235078</v>
       </c>
       <c r="I140" t="s">
         <v>11</v>
@@ -4507,26 +4539,26 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B141" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C141" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>-0.449306074582525</v>
+        <v>-1.2978416962463</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.843128119908009</v>
+        <v>-2.35311962153805</v>
       </c>
       <c r="F141" t="n">
-        <v>0.39915679353664</v>
+        <v>0.0186166440606864</v>
       </c>
       <c r="G141"/>
       <c r="H141" t="n">
-        <v>2.06523368156673</v>
+        <v>2.35311962153805</v>
       </c>
       <c r="I141" t="s">
         <v>11</v>
@@ -4534,28 +4566,28 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B142" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C142" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D142" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E142" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F142" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G142" t="n">
-        <v>0.334436097267736</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H142" t="n">
-        <v>7.28938546377511</v>
+        <v>8.44361290798045</v>
       </c>
       <c r="I142" t="s">
         <v>11</v>
@@ -4563,28 +4595,26 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B143" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D143" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.317112886110726</v>
       </c>
       <c r="E143" t="n">
-        <v>-1.93662402966198</v>
+        <v>-2.40252681339238</v>
       </c>
       <c r="F143" t="n">
-        <v>0.0527913184011619</v>
-      </c>
-      <c r="G143" t="n">
-        <v>0.435171678712281</v>
-      </c>
+        <v>0.0162822408405882</v>
+      </c>
+      <c r="G143"/>
       <c r="H143" t="n">
-        <v>3.35433121453333</v>
+        <v>5.3722132725113</v>
       </c>
       <c r="I143" t="s">
         <v>11</v>
@@ -4592,28 +4622,28 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B144" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C144" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D144" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E144" t="n">
-        <v>-2.89999694915305</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F144" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G144" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H144" t="n">
-        <v>2.89999694915305</v>
+        <v>3.52708044814411</v>
       </c>
       <c r="I144" t="s">
         <v>11</v>
@@ -4621,26 +4651,28 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B145" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="C145" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D145" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E145" t="n">
-        <v>-1.1698008416434</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F145" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G145"/>
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H145" t="n">
-        <v>2.86541516270464</v>
+        <v>3.47343294315293</v>
       </c>
       <c r="I145" t="s">
         <v>11</v>
@@ -4648,26 +4680,28 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B146" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="C146" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.858118822727544</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F146" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G146"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H146" t="n">
-        <v>2.84605816052876</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I146" t="s">
         <v>11</v>
@@ -4675,7 +4709,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B147" t="s">
         <v>12</v>
@@ -4684,46 +4718,44 @@
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E147" t="n">
-        <v>2.48507673142061</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F147" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G147" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G147"/>
       <c r="H147" t="n">
-        <v>2.48507673142061</v>
+        <v>3.0485591372467</v>
       </c>
       <c r="I147" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B148" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="n">
-        <v>-1.38550615703734</v>
+        <v>-1.07923124589441</v>
       </c>
       <c r="E148" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.02709408798513</v>
       </c>
       <c r="F148" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0426527913776698</v>
       </c>
       <c r="G148"/>
       <c r="H148" t="n">
-        <v>2.36695006782304</v>
+        <v>2.8667439514349</v>
       </c>
       <c r="I148" t="s">
         <v>11</v>
@@ -4731,26 +4763,26 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B149" t="s">
-        <v>17</v>
+        <v>31</v>
       </c>
       <c r="C149" t="n">
         <v>1</v>
       </c>
       <c r="D149" t="n">
-        <v>-0.293068543126831</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E149" t="n">
-        <v>-2.22467703206467</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F149" t="n">
-        <v>0.0261029272182321</v>
+        <v>0.00541349094466119</v>
       </c>
       <c r="G149"/>
       <c r="H149" t="n">
-        <v>2.22467703206467</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I149" t="s">
         <v>11</v>
@@ -4758,28 +4790,28 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B150" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C150" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D150" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.202266673175123</v>
       </c>
       <c r="E150" t="n">
-        <v>-2.09437444905346</v>
+        <v>-1.4500017297942</v>
       </c>
       <c r="F150" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.147058036847532</v>
       </c>
       <c r="G150" t="n">
-        <v>0.381004286040762</v>
+        <v>0.522636741025254</v>
       </c>
       <c r="H150" t="n">
-        <v>2.09437444905346</v>
+        <v>2.51147666706631</v>
       </c>
       <c r="I150" t="s">
         <v>11</v>
@@ -4787,28 +4819,26 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B151" t="s">
-        <v>67</v>
+        <v>18</v>
       </c>
       <c r="C151" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D151" t="n">
-        <v>-0.24395134664857</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E151" t="n">
-        <v>-2.08608978977804</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F151" t="n">
-        <v>0.0369704904012726</v>
-      </c>
-      <c r="G151" t="n">
-        <v>0.386605699624737</v>
-      </c>
+        <v>0.189917068187031</v>
+      </c>
+      <c r="G151"/>
       <c r="H151" t="n">
-        <v>2.08608978977804</v>
+        <v>2.27041460819781</v>
       </c>
       <c r="I151" t="s">
         <v>11</v>
@@ -4816,26 +4846,28 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B152" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C152" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="D152" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E152" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F152" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G152"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H152" t="n">
-        <v>4.73390013564608</v>
+        <v>7.55219697517558</v>
       </c>
       <c r="I152" t="s">
         <v>11</v>
@@ -4843,26 +4875,28 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B153" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C153" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D153" t="n">
-        <v>-0.293068543126831</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E153" t="n">
-        <v>-2.22467703206467</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F153" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G153"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H153" t="n">
-        <v>4.44935406412935</v>
+        <v>4.34525723111561</v>
       </c>
       <c r="I153" t="s">
         <v>11</v>
@@ -4870,55 +4904,57 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B154" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C154" t="n">
         <v>3</v>
       </c>
       <c r="D154" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E154" t="n">
-        <v>2.48507673142061</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F154" t="n">
-        <v>0.0129523513132298</v>
+        <v>0.0449216428924176</v>
       </c>
       <c r="G154" t="n">
-        <v>0.204334507786298</v>
+        <v>0.363117998309853</v>
       </c>
       <c r="H154" t="n">
-        <v>4.3042791595277</v>
+        <v>3.47343294315293</v>
       </c>
       <c r="I154" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B155" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D155" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E155" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F155" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G155"/>
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0.454783967358593</v>
+      </c>
       <c r="H155" t="n">
-        <v>3.1115168358807</v>
+        <v>3.41924769268277</v>
       </c>
       <c r="I155" t="s">
         <v>11</v>
@@ -4926,28 +4962,26 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B156" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D156" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E156" t="n">
-        <v>-2.19783241232844</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F156" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G156" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G156"/>
       <c r="H156" t="n">
-        <v>3.10820440533805</v>
+        <v>3.0485591372467</v>
       </c>
       <c r="I156" t="s">
         <v>11</v>
@@ -4955,82 +4989,80 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B157" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D157" t="n">
-        <v>0.519825670239084</v>
+        <v>-0.528075829615833</v>
       </c>
       <c r="E157" t="n">
-        <v>2.1468751925701</v>
+        <v>-1.66952321290248</v>
       </c>
       <c r="F157" t="n">
-        <v>0.0318032190620896</v>
+        <v>0.0950137339439168</v>
       </c>
       <c r="G157"/>
       <c r="H157" t="n">
-        <v>3.03614001405499</v>
+        <v>2.89169902916273</v>
       </c>
       <c r="I157" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B158" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>0.568852661112965</v>
+        <v>-0.30928968127718</v>
       </c>
       <c r="E158" t="n">
-        <v>1.69911620492032</v>
+        <v>-2.85933181562669</v>
       </c>
       <c r="F158" t="n">
-        <v>0.0892972906656036</v>
+        <v>0.00424534465393663</v>
       </c>
       <c r="G158"/>
       <c r="H158" t="n">
-        <v>2.94295559488561</v>
+        <v>2.85933181562669</v>
       </c>
       <c r="I158" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B159" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
       </c>
       <c r="D159" t="n">
-        <v>-0.359164820470093</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E159" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F159" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G159" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G159"/>
       <c r="H159" t="n">
-        <v>2.89999694915305</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I159" t="s">
         <v>11</v>
@@ -5038,82 +5070,82 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B160" t="s">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D160" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E160" t="n">
-        <v>1.0082954236419</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F160" t="n">
-        <v>0.31331265932097</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G160"/>
       <c r="H160" t="n">
-        <v>2.667698939041</v>
+        <v>2.62164897043013</v>
       </c>
       <c r="I160" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
       </c>
       <c r="C161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0.389552017255811</v>
+        <v>-1.32215169410332</v>
       </c>
       <c r="E161" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.60268118678175</v>
       </c>
       <c r="F161" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.00924979246653893</v>
       </c>
       <c r="G161"/>
       <c r="H161" t="n">
-        <v>2.60800171048597</v>
+        <v>2.60268118678175</v>
       </c>
       <c r="I161" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B162" t="s">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="C162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D162" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E162" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F162" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G162" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H162" t="n">
-        <v>2.89999694915305</v>
+        <v>3.08317150436179</v>
       </c>
       <c r="I162" t="s">
         <v>11</v>
@@ -5121,82 +5153,84 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B163" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.441365633122066</v>
       </c>
       <c r="E163" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.73524643578151</v>
       </c>
       <c r="F163" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.00623335899975071</v>
       </c>
       <c r="G163"/>
       <c r="H163" t="n">
-        <v>2.60800171048597</v>
+        <v>2.73524643578151</v>
       </c>
       <c r="I163" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B164" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D164" t="n">
-        <v>0.384791636175517</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E164" t="n">
-        <v>2.30101784326713</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F164" t="n">
-        <v>0.0213906225293496</v>
-      </c>
-      <c r="G164"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H164" t="n">
-        <v>2.30101784326713</v>
+        <v>2.49402250267319</v>
       </c>
       <c r="I164" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B165" t="s">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="C165" t="n">
         <v>1</v>
       </c>
       <c r="D165" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E165" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F165" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.0449216428924176</v>
       </c>
       <c r="G165" t="n">
-        <v>0.334436097267736</v>
+        <v>0.363117998309853</v>
       </c>
       <c r="H165" t="n">
-        <v>2.19783241232844</v>
+        <v>2.00538744474146</v>
       </c>
       <c r="I165" t="s">
         <v>11</v>
@@ -5204,28 +5238,28 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B166" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C166" t="n">
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>-0.235951201675001</v>
+        <v>-0.241963225925518</v>
       </c>
       <c r="E166" t="n">
-        <v>-1.80370004209605</v>
+        <v>-1.99948416214843</v>
       </c>
       <c r="F166" t="n">
-        <v>0.0712783429559855</v>
+        <v>0.0455559938048815</v>
       </c>
       <c r="G166" t="n">
-        <v>0.503626901967002</v>
+        <v>0.363117998309853</v>
       </c>
       <c r="H166" t="n">
-        <v>1.80370004209605</v>
+        <v>1.99948416214843</v>
       </c>
       <c r="I166" t="s">
         <v>11</v>
@@ -5233,55 +5267,55 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B167" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="C167" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D167" t="n">
-        <v>-0.272696592226143</v>
+        <v>0.203395249087213</v>
       </c>
       <c r="E167" t="n">
-        <v>-1.27637770916738</v>
+        <v>1.13556042842325</v>
       </c>
       <c r="F167" t="n">
-        <v>0.201822032086846</v>
+        <v>0.256140578123211</v>
       </c>
       <c r="G167"/>
       <c r="H167" t="n">
-        <v>1.27637770916738</v>
+        <v>1.96684835709375</v>
       </c>
       <c r="I167" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B168" t="s">
-        <v>44</v>
+        <v>77</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="n">
-        <v>-0.127705649007195</v>
+        <v>-0.186377890388803</v>
       </c>
       <c r="E168" t="n">
-        <v>-1.02792198997847</v>
+        <v>-1.76694703896333</v>
       </c>
       <c r="F168" t="n">
-        <v>0.303986524655079</v>
+        <v>0.077237098236177</v>
       </c>
       <c r="G168" t="n">
-        <v>0.763093745018922</v>
+        <v>0.446701155778302</v>
       </c>
       <c r="H168" t="n">
-        <v>1.02792198997847</v>
+        <v>1.76694703896333</v>
       </c>
       <c r="I168" t="s">
         <v>11</v>
@@ -5289,53 +5323,55 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B169" t="s">
-        <v>75</v>
+        <v>16</v>
       </c>
       <c r="C169" t="n">
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0.175437982401927</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E169" t="n">
-        <v>1.02118050571171</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F169" t="n">
-        <v>0.307168926567477</v>
-      </c>
-      <c r="G169"/>
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0.454783967358593</v>
+      </c>
       <c r="H169" t="n">
-        <v>1.02118050571171</v>
+        <v>1.70962384634138</v>
       </c>
       <c r="I169" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B170" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C170" t="n">
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>-0.121791813728833</v>
+        <v>-1.10456835562982</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.858118822727544</v>
+        <v>-1.65249622213236</v>
       </c>
       <c r="F170" t="n">
-        <v>0.390826854723006</v>
+        <v>0.0984334346398325</v>
       </c>
       <c r="G170"/>
       <c r="H170" t="n">
-        <v>0.858118822727544</v>
+        <v>1.65249622213236</v>
       </c>
       <c r="I170" t="s">
         <v>11</v>
@@ -5343,26 +5379,28 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B171" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D171" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.279829741967756</v>
       </c>
       <c r="E171" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.07190685826742</v>
       </c>
       <c r="F171" t="n">
-        <v>0.39915679353664</v>
-      </c>
-      <c r="G171"/>
+        <v>0.283761869465783</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.677405994767253</v>
+      </c>
       <c r="H171" t="n">
-        <v>0.843128119908009</v>
+        <v>1.51590521656252</v>
       </c>
       <c r="I171" t="s">
         <v>11</v>
@@ -5370,26 +5408,28 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B172" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C172" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D172" t="n">
-        <v>-0.293068543126831</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E172" t="n">
-        <v>-2.22467703206467</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F172" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G172"/>
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0.307038040099115</v>
+      </c>
       <c r="H172" t="n">
-        <v>3.14616843064579</v>
+        <v>5.34020969400319</v>
       </c>
       <c r="I172" t="s">
         <v>11</v>
@@ -5397,28 +5437,28 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B173" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E173" t="n">
-        <v>-2.09437444905346</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F173" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.00212230555625149</v>
       </c>
       <c r="G173" t="n">
-        <v>0.381004286040762</v>
+        <v>0.0865900666950608</v>
       </c>
       <c r="H173" t="n">
-        <v>2.96189275053909</v>
+        <v>5.32183150868606</v>
       </c>
       <c r="I173" t="s">
         <v>11</v>
@@ -5426,53 +5466,55 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B174" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D174" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.339642175114745</v>
       </c>
       <c r="E174" t="n">
-        <v>1.84413569483074</v>
+        <v>-2.00538744474146</v>
       </c>
       <c r="F174" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G174"/>
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H174" t="n">
-        <v>2.60800171048597</v>
+        <v>3.47343294315293</v>
       </c>
       <c r="I174" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B175" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D175" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.317112886110726</v>
       </c>
       <c r="E175" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.40252681339238</v>
       </c>
       <c r="F175" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.0162822408405882</v>
       </c>
       <c r="G175"/>
       <c r="H175" t="n">
-        <v>2.36695006782304</v>
+        <v>3.39768600346451</v>
       </c>
       <c r="I175" t="s">
         <v>11</v>
@@ -5480,26 +5522,28 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B176" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D176" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E176" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F176" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G176"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H176" t="n">
-        <v>2.20017465442735</v>
+        <v>3.0545412692842</v>
       </c>
       <c r="I176" t="s">
         <v>11</v>
@@ -5507,26 +5551,26 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B177" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="n">
-        <v>-1.0424996815487</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E177" t="n">
-        <v>-2.19286854490787</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F177" t="n">
-        <v>0.0283168515981792</v>
+        <v>0.00541349094466119</v>
       </c>
       <c r="G177"/>
       <c r="H177" t="n">
-        <v>2.19286854490787</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I177" t="s">
         <v>11</v>
@@ -5534,28 +5578,28 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B178" t="s">
-        <v>21</v>
+        <v>72</v>
       </c>
       <c r="C178" t="n">
         <v>3</v>
       </c>
       <c r="D178" t="n">
-        <v>-0.170539952646192</v>
+        <v>-0.265641519314599</v>
       </c>
       <c r="E178" t="n">
-        <v>-1.03910409537338</v>
+        <v>-1.39356722832242</v>
       </c>
       <c r="F178" t="n">
-        <v>0.298756326499217</v>
+        <v>0.163448330518012</v>
       </c>
       <c r="G178" t="n">
-        <v>0.762516147131893</v>
+        <v>0.549337767565592</v>
       </c>
       <c r="H178" t="n">
-        <v>1.79978108753958</v>
+        <v>2.41372924321737</v>
       </c>
       <c r="I178" t="s">
         <v>11</v>
@@ -5563,53 +5607,57 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B179" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D179" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.202266673175123</v>
       </c>
       <c r="E179" t="n">
-        <v>1.0082954236419</v>
+        <v>-1.4500017297942</v>
       </c>
       <c r="F179" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G179"/>
+        <v>0.147058036847532</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0.522636741025254</v>
+      </c>
       <c r="H179" t="n">
-        <v>1.74641890278696</v>
+        <v>2.0506121117394</v>
       </c>
       <c r="I179" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B180" t="s">
-        <v>69</v>
+        <v>23</v>
       </c>
       <c r="C180" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D180" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.241963225925518</v>
       </c>
       <c r="E180" t="n">
-        <v>-1.1698008416434</v>
+        <v>-1.99948416214843</v>
       </c>
       <c r="F180" t="n">
-        <v>0.242081124896929</v>
-      </c>
-      <c r="G180"/>
+        <v>0.0455559938048815</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.363117998309853</v>
+      </c>
       <c r="H180" t="n">
-        <v>1.65434821552756</v>
+        <v>1.99948416214843</v>
       </c>
       <c r="I180" t="s">
         <v>11</v>
@@ -5617,57 +5665,53 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B181" t="s">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="C181" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D181" t="n">
-        <v>-0.350420430655839</v>
+        <v>0.190647230427916</v>
       </c>
       <c r="E181" t="n">
-        <v>-1.56791478927012</v>
+        <v>1.06076660516093</v>
       </c>
       <c r="F181" t="n">
-        <v>0.116901019836926</v>
-      </c>
-      <c r="G181" t="n">
-        <v>0.581593854164919</v>
-      </c>
+        <v>0.288795982236141</v>
+      </c>
+      <c r="G181"/>
       <c r="H181" t="n">
-        <v>1.56791478927012</v>
+        <v>1.83730165511109</v>
       </c>
       <c r="I181" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B182" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D182" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.30928968127718</v>
       </c>
       <c r="E182" t="n">
-        <v>-2.89999694915305</v>
+        <v>-2.85933181562669</v>
       </c>
       <c r="F182" t="n">
-        <v>0.00373166292145953</v>
-      </c>
-      <c r="G182" t="n">
-        <v>0.0973432101530153</v>
-      </c>
+        <v>0.00424534465393663</v>
+      </c>
+      <c r="G182"/>
       <c r="H182" t="n">
-        <v>2.89999694915305</v>
+        <v>6.39366030996916</v>
       </c>
       <c r="I182" t="s">
         <v>11</v>
@@ -5675,26 +5719,26 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B183" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D183" t="n">
-        <v>-1.38550615703734</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E183" t="n">
-        <v>-2.36695006782304</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F183" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.00541349094466119</v>
       </c>
       <c r="G183"/>
       <c r="H183" t="n">
-        <v>2.36695006782304</v>
+        <v>6.21926663167053</v>
       </c>
       <c r="I183" t="s">
         <v>11</v>
@@ -5702,28 +5746,28 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B184" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D184" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E184" t="n">
-        <v>-2.09437444905346</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F184" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G184" t="n">
-        <v>0.381004286040762</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H184" t="n">
-        <v>2.09437444905346</v>
+        <v>4.18770607563074</v>
       </c>
       <c r="I184" t="s">
         <v>11</v>
@@ -5731,80 +5775,80 @@
     </row>
     <row r="185">
       <c r="A185" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B185" t="s">
-        <v>15</v>
+        <v>56</v>
       </c>
       <c r="C185" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D185" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.791912701347419</v>
       </c>
       <c r="E185" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.29038085805786</v>
       </c>
       <c r="F185" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.196918454952233</v>
       </c>
       <c r="G185"/>
       <c r="H185" t="n">
-        <v>1.84413569483074</v>
+        <v>3.64974822018412</v>
       </c>
       <c r="I185" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B186" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C186" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D186" t="n">
-        <v>0.568852661112965</v>
+        <v>0.203395249087213</v>
       </c>
       <c r="E186" t="n">
-        <v>1.69911620492032</v>
+        <v>1.13556042842325</v>
       </c>
       <c r="F186" t="n">
-        <v>0.0892972906656036</v>
+        <v>0.256140578123211</v>
       </c>
       <c r="G186"/>
       <c r="H186" t="n">
-        <v>1.69911620492032</v>
+        <v>3.40668128526976</v>
       </c>
       <c r="I186" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B187" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C187" t="n">
         <v>4</v>
       </c>
       <c r="D187" t="n">
-        <v>-0.449306074582525</v>
+        <v>-0.269232202247376</v>
       </c>
       <c r="E187" t="n">
-        <v>-0.843128119908009</v>
+        <v>-1.59528635501879</v>
       </c>
       <c r="F187" t="n">
-        <v>0.39915679353664</v>
+        <v>0.110648215490228</v>
       </c>
       <c r="G187"/>
       <c r="H187" t="n">
-        <v>1.68625623981602</v>
+        <v>3.19057271003758</v>
       </c>
       <c r="I187" t="s">
         <v>11</v>
@@ -5812,28 +5856,28 @@
     </row>
     <row r="188">
       <c r="A188" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B188" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="C188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D188" t="n">
-        <v>-0.3132774213401</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E188" t="n">
-        <v>-1.21248994342222</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F188" t="n">
-        <v>0.225324889860883</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G188" t="n">
-        <v>0.702460900247728</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H188" t="n">
-        <v>1.21248994342222</v>
+        <v>3.08317150436179</v>
       </c>
       <c r="I188" t="s">
         <v>11</v>
@@ -5841,26 +5885,28 @@
     </row>
     <row r="189">
       <c r="A189" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B189" t="s">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="C189" t="n">
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>-0.189243113934208</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E189" t="n">
-        <v>-1.06988637864807</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F189" t="n">
-        <v>0.284670455048985</v>
-      </c>
-      <c r="G189"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H189" t="n">
-        <v>1.06988637864807</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I189" t="s">
         <v>11</v>
@@ -5868,28 +5914,26 @@
     </row>
     <row r="190">
       <c r="A190" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B190" t="s">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>-0.214989848836869</v>
+        <v>-0.717496145982889</v>
       </c>
       <c r="E190" t="n">
-        <v>-1.05077682479031</v>
+        <v>-3.0485591372467</v>
       </c>
       <c r="F190" t="n">
-        <v>0.293361102116757</v>
-      </c>
-      <c r="G190" t="n">
-        <v>0.758446085972238</v>
-      </c>
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G190"/>
       <c r="H190" t="n">
-        <v>1.05077682479031</v>
+        <v>3.0485591372467</v>
       </c>
       <c r="I190" t="s">
         <v>11</v>
@@ -5897,109 +5941,113 @@
     </row>
     <row r="191">
       <c r="A191" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B191" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="C191" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D191" t="n">
-        <v>-0.141237121743142</v>
+        <v>0.152085873792625</v>
       </c>
       <c r="E191" t="n">
-        <v>-0.505075071717537</v>
+        <v>1.73888094473879</v>
       </c>
       <c r="F191" t="n">
-        <v>0.613506109324499</v>
-      </c>
-      <c r="G191"/>
+        <v>0.0820557066557046</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0.453671257672951</v>
+      </c>
       <c r="H191" t="n">
-        <v>1.01015014343507</v>
+        <v>3.01183014460096</v>
       </c>
       <c r="I191" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B192" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E192" t="n">
-        <v>1.84413569483074</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F192" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G192"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H192" t="n">
-        <v>3.19413671949818</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I192" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B193" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C193" t="n">
         <v>2</v>
       </c>
       <c r="D193" t="n">
-        <v>-0.472120445097816</v>
+        <v>0.302887223838685</v>
       </c>
       <c r="E193" t="n">
-        <v>-2.20017465442735</v>
+        <v>1.94633140021913</v>
       </c>
       <c r="F193" t="n">
-        <v>0.0277945058180277</v>
+        <v>0.0516149440670543</v>
       </c>
       <c r="G193"/>
       <c r="H193" t="n">
-        <v>3.1115168358807</v>
+        <v>2.75252826306251</v>
       </c>
       <c r="I193" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B194" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C194" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D194" t="n">
-        <v>-0.531888018405323</v>
+        <v>-0.475579071561494</v>
       </c>
       <c r="E194" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.18013147829535</v>
       </c>
       <c r="F194" t="n">
-        <v>0.0362266370333839</v>
+        <v>0.0292477170120562</v>
       </c>
       <c r="G194" t="n">
-        <v>0.381004286040762</v>
+        <v>0.307038040099115</v>
       </c>
       <c r="H194" t="n">
-        <v>2.96189275053909</v>
+        <v>2.18013147829535</v>
       </c>
       <c r="I194" t="s">
         <v>11</v>
@@ -6007,55 +6055,57 @@
     </row>
     <row r="195">
       <c r="A195" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B195" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="C195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D195" t="n">
-        <v>-0.293068543126831</v>
+        <v>0.137369704274393</v>
       </c>
       <c r="E195" t="n">
-        <v>-2.22467703206467</v>
+        <v>1.43386613239452</v>
       </c>
       <c r="F195" t="n">
-        <v>0.0261029272182321</v>
-      </c>
-      <c r="G195"/>
+        <v>0.151610468290517</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0.531584204443626</v>
+      </c>
       <c r="H195" t="n">
-        <v>2.22467703206467</v>
+        <v>2.02779293105978</v>
       </c>
       <c r="I195" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B196" t="s">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C196" t="n">
         <v>1</v>
       </c>
       <c r="D196" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.186377890388803</v>
       </c>
       <c r="E196" t="n">
-        <v>-2.19783241232844</v>
+        <v>-1.76694703896333</v>
       </c>
       <c r="F196" t="n">
-        <v>0.0279610507551714</v>
+        <v>0.077237098236177</v>
       </c>
       <c r="G196" t="n">
-        <v>0.334436097267736</v>
+        <v>0.446701155778302</v>
       </c>
       <c r="H196" t="n">
-        <v>2.19783241232844</v>
+        <v>1.76694703896333</v>
       </c>
       <c r="I196" t="s">
         <v>11</v>
@@ -6063,26 +6113,28 @@
     </row>
     <row r="197">
       <c r="A197" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B197" t="s">
-        <v>80</v>
+        <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D197" t="n">
-        <v>-0.204529625385548</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E197" t="n">
-        <v>-1.10017496528803</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F197" t="n">
-        <v>0.271255896090862</v>
-      </c>
-      <c r="G197"/>
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0.454783967358593</v>
+      </c>
       <c r="H197" t="n">
-        <v>1.55588235689368</v>
+        <v>1.70962384634138</v>
       </c>
       <c r="I197" t="s">
         <v>11</v>
@@ -6090,53 +6142,57 @@
     </row>
     <row r="198">
       <c r="A198" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B198" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="C198" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D198" t="n">
-        <v>0.202760189088342</v>
+        <v>0.0925406041267662</v>
       </c>
       <c r="E198" t="n">
-        <v>1.0082954236419</v>
+        <v>1.41621583188101</v>
       </c>
       <c r="F198" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G198"/>
+        <v>0.156712321946803</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0.540760836521722</v>
+      </c>
       <c r="H198" t="n">
-        <v>1.42594506299311</v>
+        <v>1.41621583188101</v>
       </c>
       <c r="I198" t="s">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B199" t="s">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C199" t="n">
         <v>2</v>
       </c>
       <c r="D199" t="n">
-        <v>-0.121791813728833</v>
+        <v>-0.11089531222503</v>
       </c>
       <c r="E199" t="n">
-        <v>-0.858118822727544</v>
+        <v>-0.96522896220189</v>
       </c>
       <c r="F199" t="n">
-        <v>0.390826854723006</v>
-      </c>
-      <c r="G199"/>
+        <v>0.334430143599031</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0.71540633196971</v>
+      </c>
       <c r="H199" t="n">
-        <v>1.21356327722893</v>
+        <v>1.36503988914122</v>
       </c>
       <c r="I199" t="s">
         <v>11</v>
@@ -6144,28 +6200,26 @@
     </row>
     <row r="200">
       <c r="A200" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B200" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C200" t="n">
         <v>1</v>
       </c>
       <c r="D200" t="n">
-        <v>-0.3132774213401</v>
+        <v>-0.222901509771202</v>
       </c>
       <c r="E200" t="n">
-        <v>-1.21248994342222</v>
+        <v>-1.32046963873384</v>
       </c>
       <c r="F200" t="n">
-        <v>0.225324889860883</v>
-      </c>
-      <c r="G200" t="n">
-        <v>0.702460900247728</v>
-      </c>
+        <v>0.186678266382869</v>
+      </c>
+      <c r="G200"/>
       <c r="H200" t="n">
-        <v>1.21248994342222</v>
+        <v>1.32046963873384</v>
       </c>
       <c r="I200" t="s">
         <v>11</v>
@@ -6173,26 +6227,26 @@
     </row>
     <row r="201">
       <c r="A201" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B201" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="C201" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D201" t="n">
-        <v>-0.229813761004121</v>
+        <v>-0.625101801502192</v>
       </c>
       <c r="E201" t="n">
-        <v>-0.856734680465064</v>
+        <v>-1.31082448521506</v>
       </c>
       <c r="F201" t="n">
-        <v>0.391591532264627</v>
+        <v>0.189917068187031</v>
       </c>
       <c r="G201"/>
       <c r="H201" t="n">
-        <v>1.21160580446907</v>
+        <v>1.31082448521506</v>
       </c>
       <c r="I201" t="s">
         <v>11</v>
@@ -6200,28 +6254,26 @@
     </row>
     <row r="202">
       <c r="A202" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B202" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C202" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D202" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.30928968127718</v>
       </c>
       <c r="E202" t="n">
-        <v>-2.19783241232844</v>
+        <v>-2.85933181562669</v>
       </c>
       <c r="F202" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G202" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.00424534465393663</v>
+      </c>
+      <c r="G202"/>
       <c r="H202" t="n">
-        <v>9.58012938017788</v>
+        <v>2.85933181562669</v>
       </c>
       <c r="I202" t="s">
         <v>11</v>
@@ -6229,28 +6281,26 @@
     </row>
     <row r="203">
       <c r="A203" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B203" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C203" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>-0.531888018405323</v>
+        <v>-1.13918130986185</v>
       </c>
       <c r="E203" t="n">
-        <v>-2.09437444905346</v>
+        <v>-2.78134059172229</v>
       </c>
       <c r="F203" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G203" t="n">
-        <v>0.381004286040762</v>
-      </c>
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G203"/>
       <c r="H203" t="n">
-        <v>6.28312334716039</v>
+        <v>2.78134059172229</v>
       </c>
       <c r="I203" t="s">
         <v>11</v>
@@ -6258,53 +6308,53 @@
     </row>
     <row r="204">
       <c r="A204" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B204" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D204" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.300480979410438</v>
       </c>
       <c r="E204" t="n">
-        <v>1.84413569483074</v>
+        <v>-1.92201619077215</v>
       </c>
       <c r="F204" t="n">
-        <v>0.0651633670482164</v>
+        <v>0.0546037205189322</v>
       </c>
       <c r="G204"/>
       <c r="H204" t="n">
-        <v>5.21600342097193</v>
+        <v>2.71814136409065</v>
       </c>
       <c r="I204" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B205" t="s">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="C205" t="n">
         <v>4</v>
       </c>
       <c r="D205" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.791912701347419</v>
       </c>
       <c r="E205" t="n">
-        <v>-2.36695006782304</v>
+        <v>-1.29038085805786</v>
       </c>
       <c r="F205" t="n">
-        <v>0.0179353523795742</v>
+        <v>0.196918454952233</v>
       </c>
       <c r="G205"/>
       <c r="H205" t="n">
-        <v>4.73390013564608</v>
+        <v>2.58076171611573</v>
       </c>
       <c r="I205" t="s">
         <v>11</v>
@@ -6312,28 +6362,28 @@
     </row>
     <row r="206">
       <c r="A206" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B206" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C206" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D206" t="n">
-        <v>-0.346644086928774</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E206" t="n">
-        <v>-1.93662402966198</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F206" t="n">
-        <v>0.0527913184011619</v>
+        <v>0.07780941934658</v>
       </c>
       <c r="G206" t="n">
-        <v>0.435171678712281</v>
+        <v>0.446762153706319</v>
       </c>
       <c r="H206" t="n">
-        <v>4.33042297718376</v>
+        <v>2.49402250267319</v>
       </c>
       <c r="I206" t="s">
         <v>11</v>
@@ -6341,28 +6391,28 @@
     </row>
     <row r="207">
       <c r="A207" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B207" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C207" t="n">
         <v>2</v>
       </c>
       <c r="D207" t="n">
-        <v>-0.359164820470093</v>
+        <v>-0.254026315690655</v>
       </c>
       <c r="E207" t="n">
-        <v>-2.89999694915305</v>
+        <v>-1.70962384634138</v>
       </c>
       <c r="F207" t="n">
-        <v>0.00373166292145953</v>
+        <v>0.0873354531043613</v>
       </c>
       <c r="G207" t="n">
-        <v>0.0973432101530153</v>
+        <v>0.454783967358593</v>
       </c>
       <c r="H207" t="n">
-        <v>4.10121501633284</v>
+        <v>2.41777323005244</v>
       </c>
       <c r="I207" t="s">
         <v>11</v>
@@ -6370,26 +6420,26 @@
     </row>
     <row r="208">
       <c r="A208" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B208" t="s">
-        <v>20</v>
+        <v>52</v>
       </c>
       <c r="C208" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>-0.121791813728833</v>
+        <v>-1.00528774978176</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.858118822727544</v>
+        <v>-2.36049646431568</v>
       </c>
       <c r="F208" t="n">
-        <v>0.390826854723006</v>
+        <v>0.018250492291681</v>
       </c>
       <c r="G208"/>
       <c r="H208" t="n">
-        <v>4.0249340499224</v>
+        <v>2.36049646431568</v>
       </c>
       <c r="I208" t="s">
         <v>11</v>
@@ -6397,55 +6447,53 @@
     </row>
     <row r="209">
       <c r="A209" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B209" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C209" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D209" t="n">
-        <v>-0.673259396707017</v>
+        <v>0.203395249087213</v>
       </c>
       <c r="E209" t="n">
-        <v>-1.1698008416434</v>
+        <v>1.13556042842325</v>
       </c>
       <c r="F209" t="n">
-        <v>0.242081124896929</v>
+        <v>0.256140578123211</v>
       </c>
       <c r="G209"/>
       <c r="H209" t="n">
-        <v>3.09500211046249</v>
+        <v>2.2711208568465</v>
       </c>
       <c r="I209" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B210" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C210" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D210" t="n">
-        <v>-0.244200454612073</v>
+        <v>-1.37647940076619</v>
       </c>
       <c r="E210" t="n">
-        <v>-1.16606476126988</v>
+        <v>-1.13217740569183</v>
       </c>
       <c r="F210" t="n">
-        <v>0.243588262731164</v>
-      </c>
-      <c r="G210" t="n">
-        <v>0.721615526598251</v>
-      </c>
+        <v>0.25755985717422</v>
+      </c>
+      <c r="G210"/>
       <c r="H210" t="n">
-        <v>2.60740007236651</v>
+        <v>1.96098878983977</v>
       </c>
       <c r="I210" t="s">
         <v>11</v>
@@ -6453,28 +6501,28 @@
     </row>
     <row r="211">
       <c r="A211" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B211" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="C211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D211" t="n">
-        <v>-0.235951201675001</v>
+        <v>-0.185454652651371</v>
       </c>
       <c r="E211" t="n">
-        <v>-1.80370004209605</v>
+        <v>-1.87225538924992</v>
       </c>
       <c r="F211" t="n">
-        <v>0.0712783429559855</v>
+        <v>0.06117127937628</v>
       </c>
       <c r="G211" t="n">
-        <v>0.503626901967002</v>
+        <v>0.40611938142122</v>
       </c>
       <c r="H211" t="n">
-        <v>2.55081706198515</v>
+        <v>1.87225538924992</v>
       </c>
       <c r="I211" t="s">
         <v>11</v>
@@ -6482,109 +6530,113 @@
     </row>
     <row r="212">
       <c r="A212" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B212" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C212" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>0.389552017255811</v>
+        <v>-0.382584166658979</v>
       </c>
       <c r="E212" t="n">
-        <v>1.84413569483074</v>
+        <v>-3.07256085412173</v>
       </c>
       <c r="F212" t="n">
-        <v>0.0651633670482164</v>
-      </c>
-      <c r="G212"/>
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0.0865900666950608</v>
+      </c>
       <c r="H212" t="n">
-        <v>4.51719146878823</v>
+        <v>3.07256085412173</v>
       </c>
       <c r="I212" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B213" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C213" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>0.519825670239084</v>
+        <v>-0.440704424713461</v>
       </c>
       <c r="E213" t="n">
-        <v>2.1468751925701</v>
+        <v>-1.76354022407205</v>
       </c>
       <c r="F213" t="n">
-        <v>0.0318032190620896</v>
-      </c>
-      <c r="G213"/>
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0.446762153706319</v>
+      </c>
       <c r="H213" t="n">
-        <v>4.29375038514021</v>
+        <v>1.76354022407205</v>
       </c>
       <c r="I213" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B214" t="s">
+        <v>24</v>
+      </c>
+      <c r="C214" t="n">
+        <v>1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>0.210949149380054</v>
+      </c>
+      <c r="E214" t="n">
+        <v>1.28104157000055</v>
+      </c>
+      <c r="F214" t="n">
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G214"/>
+      <c r="H214" t="n">
+        <v>1.28104157000055</v>
+      </c>
+      <c r="I214" t="s">
         <v>25</v>
-      </c>
-      <c r="C214" t="n">
-        <v>4</v>
-      </c>
-      <c r="D214" t="n">
-        <v>-0.531888018405323</v>
-      </c>
-      <c r="E214" t="n">
-        <v>-2.09437444905346</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.0362266370333839</v>
-      </c>
-      <c r="G214" t="n">
-        <v>0.381004286040762</v>
-      </c>
-      <c r="H214" t="n">
-        <v>4.18874889810692</v>
-      </c>
-      <c r="I214" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B215" t="s">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="C215" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>-0.472120445097816</v>
+        <v>-0.279829741967756</v>
       </c>
       <c r="E215" t="n">
-        <v>-2.20017465442735</v>
+        <v>-1.07190685826742</v>
       </c>
       <c r="F215" t="n">
-        <v>0.0277945058180277</v>
-      </c>
-      <c r="G215"/>
+        <v>0.283761869465783</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0.677405994767253</v>
+      </c>
       <c r="H215" t="n">
-        <v>3.81081428699347</v>
+        <v>1.07190685826742</v>
       </c>
       <c r="I215" t="s">
         <v>11</v>
@@ -6592,26 +6644,26 @@
     </row>
     <row r="216">
       <c r="A216" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B216" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="C216" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D216" t="n">
-        <v>-0.582671827903238</v>
+        <v>-0.161954876364702</v>
       </c>
       <c r="E216" t="n">
-        <v>-1.73074764769325</v>
+        <v>-1.02567454265089</v>
       </c>
       <c r="F216" t="n">
-        <v>0.0834967829299813</v>
+        <v>0.305045017836696</v>
       </c>
       <c r="G216"/>
       <c r="H216" t="n">
-        <v>2.99774286088503</v>
+        <v>1.02567454265089</v>
       </c>
       <c r="I216" t="s">
         <v>11</v>
@@ -6619,82 +6671,84 @@
     </row>
     <row r="217">
       <c r="A217" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B217" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D217" t="n">
-        <v>0.282847656074349</v>
+        <v>-0.370869206784898</v>
       </c>
       <c r="E217" t="n">
-        <v>2.48507673142061</v>
+        <v>-0.587526914204648</v>
       </c>
       <c r="F217" t="n">
-        <v>0.0129523513132298</v>
-      </c>
-      <c r="G217" t="n">
-        <v>0.204334507786298</v>
-      </c>
+        <v>0.556849880034685</v>
+      </c>
+      <c r="G217"/>
       <c r="H217" t="n">
-        <v>2.48507673142061</v>
+        <v>0.830888530327427</v>
       </c>
       <c r="I217" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B218" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="C218" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D218" t="n">
-        <v>0.202760189088342</v>
+        <v>-0.030255859194947</v>
       </c>
       <c r="E218" t="n">
-        <v>1.0082954236419</v>
+        <v>-0.357673375742895</v>
       </c>
       <c r="F218" t="n">
-        <v>0.31331265932097</v>
-      </c>
-      <c r="G218"/>
+        <v>0.720587759822087</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0.923084868347736</v>
+      </c>
       <c r="H218" t="n">
-        <v>2.46980929790606</v>
+        <v>0.71534675148579</v>
       </c>
       <c r="I218" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B219" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="C219" t="n">
         <v>1</v>
       </c>
       <c r="D219" t="n">
-        <v>-1.38550615703734</v>
+        <v>-0.0477851818645616</v>
       </c>
       <c r="E219" t="n">
-        <v>-2.36695006782304</v>
+        <v>-0.405353775737904</v>
       </c>
       <c r="F219" t="n">
-        <v>0.0179353523795742</v>
-      </c>
-      <c r="G219"/>
+        <v>0.685217483368185</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0.901860784269583</v>
+      </c>
       <c r="H219" t="n">
-        <v>2.36695006782304</v>
+        <v>0.405353775737904</v>
       </c>
       <c r="I219" t="s">
         <v>11</v>
@@ -6702,28 +6756,26 @@
     </row>
     <row r="220">
       <c r="A220" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B220" t="s">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D220" t="n">
-        <v>-0.467382365575886</v>
+        <v>-0.0265334916610935</v>
       </c>
       <c r="E220" t="n">
-        <v>-2.19783241232844</v>
+        <v>-0.131268152725928</v>
       </c>
       <c r="F220" t="n">
-        <v>0.0279610507551714</v>
-      </c>
-      <c r="G220" t="n">
-        <v>0.334436097267736</v>
-      </c>
+        <v>0.895563184199726</v>
+      </c>
+      <c r="G220"/>
       <c r="H220" t="n">
-        <v>2.19783241232844</v>
+        <v>0.371282403785339</v>
       </c>
       <c r="I220" t="s">
         <v>11</v>
@@ -6731,28 +6783,852 @@
     </row>
     <row r="221">
       <c r="A221" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B221" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D221" t="n">
-        <v>-0.673259396707017</v>
+        <v>-0.0749436558670191</v>
       </c>
       <c r="E221" t="n">
-        <v>-1.1698008416434</v>
+        <v>-0.329212623811751</v>
       </c>
       <c r="F221" t="n">
-        <v>0.242081124896929</v>
+        <v>0.7419949818703</v>
       </c>
       <c r="G221"/>
       <c r="H221" t="n">
-        <v>2.02615449246321</v>
+        <v>0.329212623811751</v>
       </c>
       <c r="I221" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>90</v>
+      </c>
+      <c r="B222" t="s">
+        <v>13</v>
+      </c>
+      <c r="C222" t="n">
+        <v>1</v>
+      </c>
+      <c r="D222" t="n">
+        <v>-0.30928968127718</v>
+      </c>
+      <c r="E222" t="n">
+        <v>-2.85933181562669</v>
+      </c>
+      <c r="F222" t="n">
+        <v>0.00424534465393663</v>
+      </c>
+      <c r="G222"/>
+      <c r="H222" t="n">
+        <v>2.85933181562669</v>
+      </c>
+      <c r="I222" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>90</v>
+      </c>
+      <c r="B223" t="s">
+        <v>14</v>
+      </c>
+      <c r="C223" t="n">
+        <v>1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>-0.441365633122066</v>
+      </c>
+      <c r="E223" t="n">
+        <v>-2.73524643578151</v>
+      </c>
+      <c r="F223" t="n">
+        <v>0.00623335899975071</v>
+      </c>
+      <c r="G223"/>
+      <c r="H223" t="n">
+        <v>2.73524643578151</v>
+      </c>
+      <c r="I223" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>90</v>
+      </c>
+      <c r="B224" t="s">
+        <v>45</v>
+      </c>
+      <c r="C224" t="n">
+        <v>1</v>
+      </c>
+      <c r="D224" t="n">
+        <v>-0.317112886110726</v>
+      </c>
+      <c r="E224" t="n">
+        <v>-2.40252681339238</v>
+      </c>
+      <c r="F224" t="n">
+        <v>0.0162822408405882</v>
+      </c>
+      <c r="G224"/>
+      <c r="H224" t="n">
+        <v>2.40252681339238</v>
+      </c>
+      <c r="I224" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>90</v>
+      </c>
+      <c r="B225" t="s">
+        <v>56</v>
+      </c>
+      <c r="C225" t="n">
+        <v>3</v>
+      </c>
+      <c r="D225" t="n">
+        <v>-0.791912701347419</v>
+      </c>
+      <c r="E225" t="n">
+        <v>-1.29038085805786</v>
+      </c>
+      <c r="F225" t="n">
+        <v>0.196918454952233</v>
+      </c>
+      <c r="G225"/>
+      <c r="H225" t="n">
+        <v>2.23500520727054</v>
+      </c>
+      <c r="I225" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>90</v>
+      </c>
+      <c r="B226" t="s">
+        <v>33</v>
+      </c>
+      <c r="C226" t="n">
+        <v>1</v>
+      </c>
+      <c r="D226" t="n">
+        <v>-1.07923124589441</v>
+      </c>
+      <c r="E226" t="n">
+        <v>-2.02709408798513</v>
+      </c>
+      <c r="F226" t="n">
+        <v>0.0426527913776698</v>
+      </c>
+      <c r="G226"/>
+      <c r="H226" t="n">
+        <v>2.02709408798513</v>
+      </c>
+      <c r="I226" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>90</v>
+      </c>
+      <c r="B227" t="s">
+        <v>35</v>
+      </c>
+      <c r="C227" t="n">
+        <v>3</v>
+      </c>
+      <c r="D227" t="n">
+        <v>0.203395249087213</v>
+      </c>
+      <c r="E227" t="n">
+        <v>1.13556042842325</v>
+      </c>
+      <c r="F227" t="n">
+        <v>0.256140578123211</v>
+      </c>
+      <c r="G227"/>
+      <c r="H227" t="n">
+        <v>1.96684835709375</v>
+      </c>
+      <c r="I227" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>90</v>
+      </c>
+      <c r="B228" t="s">
+        <v>46</v>
+      </c>
+      <c r="C228" t="n">
+        <v>1</v>
+      </c>
+      <c r="D228" t="n">
+        <v>-0.300480979410438</v>
+      </c>
+      <c r="E228" t="n">
+        <v>-1.92201619077215</v>
+      </c>
+      <c r="F228" t="n">
+        <v>0.0546037205189322</v>
+      </c>
+      <c r="G228"/>
+      <c r="H228" t="n">
+        <v>1.92201619077215</v>
+      </c>
+      <c r="I228" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>90</v>
+      </c>
+      <c r="B229" t="s">
+        <v>91</v>
+      </c>
+      <c r="C229" t="n">
+        <v>2</v>
+      </c>
+      <c r="D229" t="n">
+        <v>-0.26020619774606</v>
+      </c>
+      <c r="E229" t="n">
+        <v>-1.32509828986016</v>
+      </c>
+      <c r="F229" t="n">
+        <v>0.185138553282214</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0.58038648407547</v>
+      </c>
+      <c r="H229" t="n">
+        <v>1.87397197299764</v>
+      </c>
+      <c r="I229" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>90</v>
+      </c>
+      <c r="B230" t="s">
+        <v>84</v>
+      </c>
+      <c r="C230" t="n">
+        <v>2</v>
+      </c>
+      <c r="D230" t="n">
+        <v>-0.222901509771202</v>
+      </c>
+      <c r="E230" t="n">
+        <v>-1.32046963873384</v>
+      </c>
+      <c r="F230" t="n">
+        <v>0.186678266382869</v>
+      </c>
+      <c r="G230"/>
+      <c r="H230" t="n">
+        <v>1.8674260717993</v>
+      </c>
+      <c r="I230" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>90</v>
+      </c>
+      <c r="B231" t="s">
+        <v>24</v>
+      </c>
+      <c r="C231" t="n">
+        <v>2</v>
+      </c>
+      <c r="D231" t="n">
+        <v>0.210949149380054</v>
+      </c>
+      <c r="E231" t="n">
+        <v>1.28104157000055</v>
+      </c>
+      <c r="F231" t="n">
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G231"/>
+      <c r="H231" t="n">
+        <v>1.8116663622585</v>
+      </c>
+      <c r="I231" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>92</v>
+      </c>
+      <c r="B232" t="s">
+        <v>19</v>
+      </c>
+      <c r="C232" t="n">
+        <v>24</v>
+      </c>
+      <c r="D232" t="n">
+        <v>-0.475579071561494</v>
+      </c>
+      <c r="E232" t="n">
+        <v>-2.18013147829535</v>
+      </c>
+      <c r="F232" t="n">
+        <v>0.0292477170120562</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0.307038040099115</v>
+      </c>
+      <c r="H232" t="n">
+        <v>10.6804193880064</v>
+      </c>
+      <c r="I232" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>92</v>
+      </c>
+      <c r="B233" t="s">
+        <v>10</v>
+      </c>
+      <c r="C233" t="n">
+        <v>4</v>
+      </c>
+      <c r="D233" t="n">
+        <v>-0.382584166658979</v>
+      </c>
+      <c r="E233" t="n">
+        <v>-3.07256085412173</v>
+      </c>
+      <c r="F233" t="n">
+        <v>0.00212230555625149</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0.0865900666950608</v>
+      </c>
+      <c r="H233" t="n">
+        <v>6.14512170824346</v>
+      </c>
+      <c r="I233" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>92</v>
+      </c>
+      <c r="B234" t="s">
+        <v>22</v>
+      </c>
+      <c r="C234" t="n">
+        <v>8</v>
+      </c>
+      <c r="D234" t="n">
+        <v>-0.440704424713461</v>
+      </c>
+      <c r="E234" t="n">
+        <v>-1.76354022407205</v>
+      </c>
+      <c r="F234" t="n">
+        <v>0.07780941934658</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0.446762153706319</v>
+      </c>
+      <c r="H234" t="n">
+        <v>4.98804500534637</v>
+      </c>
+      <c r="I234" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>92</v>
+      </c>
+      <c r="B235" t="s">
+        <v>34</v>
+      </c>
+      <c r="C235" t="n">
+        <v>6</v>
+      </c>
+      <c r="D235" t="n">
+        <v>-0.339642175114745</v>
+      </c>
+      <c r="E235" t="n">
+        <v>-2.00538744474146</v>
+      </c>
+      <c r="F235" t="n">
+        <v>0.0449216428924176</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0.363117998309853</v>
+      </c>
+      <c r="H235" t="n">
+        <v>4.91217597620037</v>
+      </c>
+      <c r="I235" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>92</v>
+      </c>
+      <c r="B236" t="s">
+        <v>31</v>
+      </c>
+      <c r="C236" t="n">
+        <v>3</v>
+      </c>
+      <c r="D236" t="n">
+        <v>-1.13918130986185</v>
+      </c>
+      <c r="E236" t="n">
+        <v>-2.78134059172229</v>
+      </c>
+      <c r="F236" t="n">
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G236"/>
+      <c r="H236" t="n">
+        <v>4.8174232180167</v>
+      </c>
+      <c r="I236" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>92</v>
+      </c>
+      <c r="B237" t="s">
+        <v>12</v>
+      </c>
+      <c r="C237" t="n">
+        <v>2</v>
+      </c>
+      <c r="D237" t="n">
+        <v>-0.717496145982889</v>
+      </c>
+      <c r="E237" t="n">
+        <v>-3.0485591372467</v>
+      </c>
+      <c r="F237" t="n">
+        <v>0.00229941650586847</v>
+      </c>
+      <c r="G237"/>
+      <c r="H237" t="n">
+        <v>4.3113136775907</v>
+      </c>
+      <c r="I237" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>92</v>
+      </c>
+      <c r="B238" t="s">
+        <v>18</v>
+      </c>
+      <c r="C238" t="n">
+        <v>9</v>
+      </c>
+      <c r="D238" t="n">
+        <v>-0.625101801502192</v>
+      </c>
+      <c r="E238" t="n">
+        <v>-1.31082448521506</v>
+      </c>
+      <c r="F238" t="n">
+        <v>0.189917068187031</v>
+      </c>
+      <c r="G238"/>
+      <c r="H238" t="n">
+        <v>3.93247345564519</v>
+      </c>
+      <c r="I238" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>92</v>
+      </c>
+      <c r="B239" t="s">
+        <v>45</v>
+      </c>
+      <c r="C239" t="n">
+        <v>2</v>
+      </c>
+      <c r="D239" t="n">
+        <v>-0.317112886110726</v>
+      </c>
+      <c r="E239" t="n">
+        <v>-2.40252681339238</v>
+      </c>
+      <c r="F239" t="n">
+        <v>0.0162822408405882</v>
+      </c>
+      <c r="G239"/>
+      <c r="H239" t="n">
+        <v>3.39768600346451</v>
+      </c>
+      <c r="I239" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>92</v>
+      </c>
+      <c r="B240" t="s">
+        <v>24</v>
+      </c>
+      <c r="C240" t="n">
+        <v>7</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.210949149380054</v>
+      </c>
+      <c r="E240" t="n">
+        <v>1.28104157000055</v>
+      </c>
+      <c r="F240" t="n">
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G240"/>
+      <c r="H240" t="n">
+        <v>3.3893174133572</v>
+      </c>
+      <c r="I240" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>92</v>
+      </c>
+      <c r="B241" t="s">
+        <v>57</v>
+      </c>
+      <c r="C241" t="n">
+        <v>3</v>
+      </c>
+      <c r="D241" t="n">
+        <v>-0.357413540274438</v>
+      </c>
+      <c r="E241" t="n">
+        <v>-1.79254788571914</v>
+      </c>
+      <c r="F241" t="n">
+        <v>0.0730452457883126</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0.441975579433005</v>
+      </c>
+      <c r="H241" t="n">
+        <v>3.10478401306573</v>
+      </c>
+      <c r="I241" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>93</v>
+      </c>
+      <c r="B242" t="s">
+        <v>94</v>
+      </c>
+      <c r="C242" t="n">
+        <v>4</v>
+      </c>
+      <c r="D242" t="n">
+        <v>0.36711847986094</v>
+      </c>
+      <c r="E242" t="n">
+        <v>1.79197564797351</v>
+      </c>
+      <c r="F242" t="n">
+        <v>0.0731368669347501</v>
+      </c>
+      <c r="G242"/>
+      <c r="H242" t="n">
+        <v>3.58395129594701</v>
+      </c>
+      <c r="I242" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>93</v>
+      </c>
+      <c r="B243" t="s">
+        <v>33</v>
+      </c>
+      <c r="C243" t="n">
+        <v>3</v>
+      </c>
+      <c r="D243" t="n">
+        <v>-1.07923124589441</v>
+      </c>
+      <c r="E243" t="n">
+        <v>-2.02709408798513</v>
+      </c>
+      <c r="F243" t="n">
+        <v>0.0426527913776698</v>
+      </c>
+      <c r="G243"/>
+      <c r="H243" t="n">
+        <v>3.51102995211275</v>
+      </c>
+      <c r="I243" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>93</v>
+      </c>
+      <c r="B244" t="s">
+        <v>16</v>
+      </c>
+      <c r="C244" t="n">
+        <v>4</v>
+      </c>
+      <c r="D244" t="n">
+        <v>-0.254026315690655</v>
+      </c>
+      <c r="E244" t="n">
+        <v>-1.70962384634138</v>
+      </c>
+      <c r="F244" t="n">
+        <v>0.0873354531043613</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0.454783967358593</v>
+      </c>
+      <c r="H244" t="n">
+        <v>3.41924769268277</v>
+      </c>
+      <c r="I244" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>93</v>
+      </c>
+      <c r="B245" t="s">
+        <v>17</v>
+      </c>
+      <c r="C245" t="n">
+        <v>2</v>
+      </c>
+      <c r="D245" t="n">
+        <v>-1.2978416962463</v>
+      </c>
+      <c r="E245" t="n">
+        <v>-2.35311962153805</v>
+      </c>
+      <c r="F245" t="n">
+        <v>0.0186166440606864</v>
+      </c>
+      <c r="G245"/>
+      <c r="H245" t="n">
+        <v>3.32781368266535</v>
+      </c>
+      <c r="I245" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>93</v>
+      </c>
+      <c r="B246" t="s">
+        <v>35</v>
+      </c>
+      <c r="C246" t="n">
+        <v>7</v>
+      </c>
+      <c r="D246" t="n">
+        <v>0.203395249087213</v>
+      </c>
+      <c r="E246" t="n">
+        <v>1.13556042842325</v>
+      </c>
+      <c r="F246" t="n">
+        <v>0.256140578123211</v>
+      </c>
+      <c r="G246"/>
+      <c r="H246" t="n">
+        <v>3.00441049229389</v>
+      </c>
+      <c r="I246" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>93</v>
+      </c>
+      <c r="B247" t="s">
+        <v>18</v>
+      </c>
+      <c r="C247" t="n">
+        <v>5</v>
+      </c>
+      <c r="D247" t="n">
+        <v>-0.625101801502192</v>
+      </c>
+      <c r="E247" t="n">
+        <v>-1.31082448521506</v>
+      </c>
+      <c r="F247" t="n">
+        <v>0.189917068187031</v>
+      </c>
+      <c r="G247"/>
+      <c r="H247" t="n">
+        <v>2.93109265551205</v>
+      </c>
+      <c r="I247" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>93</v>
+      </c>
+      <c r="B248" t="s">
+        <v>50</v>
+      </c>
+      <c r="C248" t="n">
+        <v>3</v>
+      </c>
+      <c r="D248" t="n">
+        <v>-0.528075829615833</v>
+      </c>
+      <c r="E248" t="n">
+        <v>-1.66952321290248</v>
+      </c>
+      <c r="F248" t="n">
+        <v>0.0950137339439168</v>
+      </c>
+      <c r="G248"/>
+      <c r="H248" t="n">
+        <v>2.89169902916273</v>
+      </c>
+      <c r="I248" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>93</v>
+      </c>
+      <c r="B249" t="s">
+        <v>56</v>
+      </c>
+      <c r="C249" t="n">
+        <v>5</v>
+      </c>
+      <c r="D249" t="n">
+        <v>-0.791912701347419</v>
+      </c>
+      <c r="E249" t="n">
+        <v>-1.29038085805786</v>
+      </c>
+      <c r="F249" t="n">
+        <v>0.196918454952233</v>
+      </c>
+      <c r="G249"/>
+      <c r="H249" t="n">
+        <v>2.88537931548189</v>
+      </c>
+      <c r="I249" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>93</v>
+      </c>
+      <c r="B250" t="s">
+        <v>24</v>
+      </c>
+      <c r="C250" t="n">
+        <v>5</v>
+      </c>
+      <c r="D250" t="n">
+        <v>0.210949149380054</v>
+      </c>
+      <c r="E250" t="n">
+        <v>1.28104157000055</v>
+      </c>
+      <c r="F250" t="n">
+        <v>0.200179065237641</v>
+      </c>
+      <c r="G250"/>
+      <c r="H250" t="n">
+        <v>2.86449603252429</v>
+      </c>
+      <c r="I250" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>93</v>
+      </c>
+      <c r="B251" t="s">
+        <v>31</v>
+      </c>
+      <c r="C251" t="n">
+        <v>1</v>
+      </c>
+      <c r="D251" t="n">
+        <v>-1.13918130986185</v>
+      </c>
+      <c r="E251" t="n">
+        <v>-2.78134059172229</v>
+      </c>
+      <c r="F251" t="n">
+        <v>0.00541349094466119</v>
+      </c>
+      <c r="G251"/>
+      <c r="H251" t="n">
+        <v>2.78134059172229</v>
+      </c>
+      <c r="I251" t="s">
         <v>11</v>
       </c>
     </row>
